--- a/src/DashboardApp/statistics_RCE.xlsx
+++ b/src/DashboardApp/statistics_RCE.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15385772</v>
+        <v>20983778</v>
       </c>
       <c r="C2" t="n">
-        <v>119016356.6</v>
+        <v>70151493.40000001</v>
       </c>
       <c r="D2" t="n">
-        <v>280563725</v>
+        <v>136864938</v>
       </c>
       <c r="E2" t="n">
-        <v>82228112.34549962</v>
+        <v>41920162.25820207</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13163853</v>
+        <v>20983778</v>
       </c>
       <c r="C3" t="n">
-        <v>69627128.59999999</v>
+        <v>44566997.4</v>
       </c>
       <c r="D3" t="n">
-        <v>140003443</v>
+        <v>91368435</v>
       </c>
       <c r="E3" t="n">
-        <v>40742855.59513031</v>
+        <v>22880008.87562323</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1863171</v>
+        <v>20983778</v>
       </c>
       <c r="C4" t="n">
-        <v>36524835.1</v>
+        <v>29319184.1</v>
       </c>
       <c r="D4" t="n">
-        <v>94424941</v>
+        <v>49493395</v>
       </c>
       <c r="E4" t="n">
-        <v>33092330.79680246</v>
+        <v>12398685.38537491</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1169650</v>
+        <v>15690106</v>
       </c>
       <c r="C5" t="n">
-        <v>7488340.8</v>
+        <v>22458617.1</v>
       </c>
       <c r="D5" t="n">
-        <v>13800671</v>
+        <v>34655890</v>
       </c>
       <c r="E5" t="n">
-        <v>5912197.638712255</v>
+        <v>5970688.655275478</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1139669</v>
+        <v>14964283</v>
       </c>
       <c r="C6" t="n">
-        <v>2255713.6</v>
+        <v>17139683</v>
       </c>
       <c r="D6" t="n">
-        <v>10709890</v>
+        <v>20983778</v>
       </c>
       <c r="E6" t="n">
-        <v>2827980.781314159</v>
+        <v>2532078.236471377</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1121569</v>
+        <v>12915050</v>
       </c>
       <c r="C7" t="n">
-        <v>1242173.1</v>
+        <v>15095676.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1863171</v>
+        <v>20257955</v>
       </c>
       <c r="E7" t="n">
-        <v>219703.4275401501</v>
+        <v>2073078.917717857</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1120066</v>
+        <v>12915050</v>
       </c>
       <c r="C8" t="n">
-        <v>1138766.5</v>
+        <v>14165320.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1169650</v>
+        <v>19199168</v>
       </c>
       <c r="E8" t="n">
-        <v>15237.35710843583</v>
+        <v>1935233.794399532</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1120066</v>
+        <v>12049425</v>
       </c>
       <c r="C9" t="n">
-        <v>1133377.2</v>
+        <v>12741925</v>
       </c>
       <c r="D9" t="n">
-        <v>1157969</v>
+        <v>12915050</v>
       </c>
       <c r="E9" t="n">
-        <v>14637.4512180229</v>
+        <v>346250</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>987053</v>
+        <v>12049425</v>
       </c>
       <c r="C10" t="n">
-        <v>1082272.3</v>
+        <v>12482237.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1138166</v>
+        <v>12915050</v>
       </c>
       <c r="E10" t="n">
-        <v>62550.66180313363</v>
+        <v>432812.5</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>660834</v>
+        <v>8923365</v>
       </c>
       <c r="C11" t="n">
-        <v>985604.3</v>
+        <v>11902719.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1138166</v>
+        <v>16545893</v>
       </c>
       <c r="E11" t="n">
-        <v>171876.6154496009</v>
+        <v>2015213.977716483</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>660834</v>
+        <v>8387244</v>
       </c>
       <c r="C12" t="n">
-        <v>825333.5</v>
+        <v>9383650.4</v>
       </c>
       <c r="D12" t="n">
-        <v>987053</v>
+        <v>12021525</v>
       </c>
       <c r="E12" t="n">
-        <v>161767.2818596208</v>
+        <v>1212246.653633096</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>538814</v>
+        <v>7731721</v>
       </c>
       <c r="C13" t="n">
-        <v>680052.8</v>
+        <v>8417435.699999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1039062</v>
+        <v>8951465</v>
       </c>
       <c r="E13" t="n">
-        <v>130378.6324708156</v>
+        <v>417618.7806710924</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>524802</v>
+        <v>6573494</v>
       </c>
       <c r="C14" t="n">
-        <v>604083.6</v>
+        <v>7893239.9</v>
       </c>
       <c r="D14" t="n">
-        <v>676233</v>
+        <v>8923365</v>
       </c>
       <c r="E14" t="n">
-        <v>61427.04139416125</v>
+        <v>690093.0823650459</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>524007</v>
+        <v>6027773</v>
       </c>
       <c r="C15" t="n">
-        <v>544169.4</v>
+        <v>7070176.9</v>
       </c>
       <c r="D15" t="n">
-        <v>660834</v>
+        <v>8383749</v>
       </c>
       <c r="E15" t="n">
-        <v>39547.08345048974</v>
+        <v>642025.7589244298</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>298585</v>
+        <v>6004273</v>
       </c>
       <c r="C16" t="n">
-        <v>480721.3</v>
+        <v>6352477.6</v>
       </c>
       <c r="D16" t="n">
-        <v>538814</v>
+        <v>6601594</v>
       </c>
       <c r="E16" t="n">
-        <v>91167.6550494198</v>
+        <v>275365.0594691345</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>298585</v>
+        <v>5077248</v>
       </c>
       <c r="C17" t="n">
-        <v>395624.7</v>
+        <v>5899313.3</v>
       </c>
       <c r="D17" t="n">
-        <v>582616</v>
+        <v>6573494</v>
       </c>
       <c r="E17" t="n">
-        <v>117921.0835483206</v>
+        <v>491774.0091893938</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>298585</v>
+        <v>4349025</v>
       </c>
       <c r="C18" t="n">
-        <v>322517.2</v>
+        <v>5085317.5</v>
       </c>
       <c r="D18" t="n">
-        <v>537907</v>
+        <v>6004273</v>
       </c>
       <c r="E18" t="n">
-        <v>71796.60000000001</v>
+        <v>541402.5637015861</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>112758</v>
+        <v>3371385</v>
       </c>
       <c r="C19" t="n">
-        <v>280002.3</v>
+        <v>4644721.4</v>
       </c>
       <c r="D19" t="n">
-        <v>298585</v>
+        <v>6027773</v>
       </c>
       <c r="E19" t="n">
-        <v>55748.10000000001</v>
+        <v>763575.6355302597</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112758</v>
+        <v>2971366</v>
       </c>
       <c r="C20" t="n">
-        <v>238355.7</v>
+        <v>3724467.8</v>
       </c>
       <c r="D20" t="n">
-        <v>298585</v>
+        <v>4691029</v>
       </c>
       <c r="E20" t="n">
-        <v>83263.10788464479</v>
+        <v>654656.9731090933</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>112758</v>
+        <v>681611</v>
       </c>
       <c r="C21" t="n">
-        <v>50737922.4</v>
+        <v>55615934</v>
       </c>
       <c r="D21" t="n">
-        <v>117630836</v>
+        <v>168088926</v>
       </c>
       <c r="E21" t="n">
-        <v>36626796.77146918</v>
+        <v>53273276.41426826</v>
       </c>
     </row>
     <row r="22">
@@ -800,16 +800,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>112758</v>
+        <v>681611</v>
       </c>
       <c r="C22" t="n">
-        <v>15897283.4</v>
+        <v>14764189.9</v>
       </c>
       <c r="D22" t="n">
-        <v>42522334</v>
+        <v>58222357</v>
       </c>
       <c r="E22" t="n">
-        <v>14641654.43837813</v>
+        <v>19816911.44298379</v>
       </c>
     </row>
     <row r="23">
@@ -817,16 +817,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>72824</v>
+        <v>681611</v>
       </c>
       <c r="C23" t="n">
-        <v>1932155.1</v>
+        <v>1178742.8</v>
       </c>
       <c r="D23" t="n">
-        <v>4961916</v>
+        <v>2939079</v>
       </c>
       <c r="E23" t="n">
-        <v>2265363.921844455</v>
+        <v>798546.3475142567</v>
       </c>
     </row>
     <row r="24">
@@ -834,16 +834,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>72824</v>
+        <v>528691</v>
       </c>
       <c r="C24" t="n">
-        <v>134250.6</v>
+        <v>646026.1</v>
       </c>
       <c r="D24" t="n">
-        <v>312273</v>
+        <v>694311</v>
       </c>
       <c r="E24" t="n">
-        <v>91744.58947556526</v>
+        <v>61806.07607743757</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +851,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>68621</v>
+        <v>223658</v>
       </c>
       <c r="C25" t="n">
-        <v>96218.10000000001</v>
+        <v>508059.8</v>
       </c>
       <c r="D25" t="n">
-        <v>312273</v>
+        <v>681611</v>
       </c>
       <c r="E25" t="n">
-        <v>72062.90590511875</v>
+        <v>153631.2359644353</v>
       </c>
     </row>
     <row r="26">
@@ -868,16 +868,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>68424</v>
+        <v>223658</v>
       </c>
       <c r="C26" t="n">
-        <v>71252.60000000001</v>
+        <v>344509.9</v>
       </c>
       <c r="D26" t="n">
-        <v>79026</v>
+        <v>541391</v>
       </c>
       <c r="E26" t="n">
-        <v>3698.82517023987</v>
+        <v>128883.6253668013</v>
       </c>
     </row>
     <row r="27">
@@ -885,16 +885,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>36917</v>
+        <v>157949</v>
       </c>
       <c r="C27" t="n">
-        <v>62561.5</v>
+        <v>222407.5</v>
       </c>
       <c r="D27" t="n">
-        <v>72824</v>
+        <v>278667</v>
       </c>
       <c r="E27" t="n">
-        <v>13012.46437266977</v>
+        <v>35349.58279598219</v>
       </c>
     </row>
     <row r="28">
@@ -902,16 +902,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>36114</v>
+        <v>101035</v>
       </c>
       <c r="C28" t="n">
-        <v>52548.7</v>
+        <v>177348.9</v>
       </c>
       <c r="D28" t="n">
-        <v>72824</v>
+        <v>223658</v>
       </c>
       <c r="E28" t="n">
-        <v>16071.03580389267</v>
+        <v>45753.09386358479</v>
       </c>
     </row>
     <row r="29">
@@ -919,16 +919,16 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>36114</v>
+        <v>40120</v>
       </c>
       <c r="C29" t="n">
-        <v>36354.9</v>
+        <v>115306.1</v>
       </c>
       <c r="D29" t="n">
-        <v>36917</v>
+        <v>223658</v>
       </c>
       <c r="E29" t="n">
-        <v>367.9808283049539</v>
+        <v>55450.39789839204</v>
       </c>
     </row>
     <row r="30">
@@ -936,16 +936,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>21409</v>
+        <v>40120</v>
       </c>
       <c r="C30" t="n">
-        <v>33032.8</v>
+        <v>63784.8</v>
       </c>
       <c r="D30" t="n">
-        <v>39915</v>
+        <v>119031</v>
       </c>
       <c r="E30" t="n">
-        <v>6156.743665282809</v>
+        <v>30840.84147619841</v>
       </c>
     </row>
     <row r="31">
@@ -953,16 +953,16 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>16206</v>
+        <v>40120</v>
       </c>
       <c r="C31" t="n">
-        <v>27010.6</v>
+        <v>49991.6</v>
       </c>
       <c r="D31" t="n">
-        <v>36114</v>
+        <v>135736</v>
       </c>
       <c r="E31" t="n">
-        <v>8020.787345391973</v>
+        <v>28596.40640080498</v>
       </c>
     </row>
     <row r="32">
@@ -970,16 +970,16 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>16206</v>
+        <v>40120</v>
       </c>
       <c r="C32" t="n">
-        <v>20058.1</v>
+        <v>40430</v>
       </c>
       <c r="D32" t="n">
-        <v>23509</v>
+        <v>43220</v>
       </c>
       <c r="E32" t="n">
-        <v>2595.656350521001</v>
+        <v>930</v>
       </c>
     </row>
     <row r="33">
@@ -987,16 +987,16 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>11703</v>
+        <v>26515</v>
       </c>
       <c r="C33" t="n">
-        <v>17666.7</v>
+        <v>37558.9</v>
       </c>
       <c r="D33" t="n">
-        <v>21409</v>
+        <v>41719</v>
       </c>
       <c r="E33" t="n">
-        <v>3678.967383655365</v>
+        <v>5542.170323077413</v>
       </c>
     </row>
     <row r="34">
@@ -1004,16 +1004,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>11703</v>
+        <v>12510</v>
       </c>
       <c r="C34" t="n">
-        <v>15075.2</v>
+        <v>30516.5</v>
       </c>
       <c r="D34" t="n">
-        <v>19007</v>
+        <v>40120</v>
       </c>
       <c r="E34" t="n">
-        <v>2737.563690583289</v>
+        <v>10759.36871986456</v>
       </c>
     </row>
     <row r="35">
@@ -1021,16 +1021,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>11703</v>
+        <v>8507</v>
       </c>
       <c r="C35" t="n">
-        <v>19515.7</v>
+        <v>21122.9</v>
       </c>
       <c r="D35" t="n">
-        <v>68617</v>
+        <v>40120</v>
       </c>
       <c r="E35" t="n">
-        <v>16611.90665185667</v>
+        <v>11515.42803763716</v>
       </c>
     </row>
     <row r="36">
@@ -1038,16 +1038,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>8103</v>
+        <v>8507</v>
       </c>
       <c r="C36" t="n">
-        <v>11303.1</v>
+        <v>9727.9</v>
       </c>
       <c r="D36" t="n">
-        <v>14504</v>
+        <v>12510</v>
       </c>
       <c r="E36" t="n">
-        <v>1797.954418220884</v>
+        <v>1621.636793489837</v>
       </c>
     </row>
     <row r="37">
@@ -1055,16 +1055,16 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>8103</v>
+        <v>8507</v>
       </c>
       <c r="C37" t="n">
-        <v>8823</v>
+        <v>8847</v>
       </c>
       <c r="D37" t="n">
-        <v>11703</v>
+        <v>10207</v>
       </c>
       <c r="E37" t="n">
-        <v>1440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>7702</v>
+        <v>8507</v>
       </c>
       <c r="C38" t="n">
-        <v>8252.700000000001</v>
+        <v>8507</v>
       </c>
       <c r="D38" t="n">
-        <v>10504</v>
+        <v>8507</v>
       </c>
       <c r="E38" t="n">
-        <v>774.1126597595469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1089,16 +1089,16 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>7702</v>
+        <v>3304</v>
       </c>
       <c r="C39" t="n">
-        <v>8012.4</v>
+        <v>7506.1</v>
       </c>
       <c r="D39" t="n">
-        <v>9503</v>
+        <v>10207</v>
       </c>
       <c r="E39" t="n">
-        <v>526.5474717440014</v>
+        <v>2339.534460100983</v>
       </c>
     </row>
     <row r="40">
@@ -1106,16 +1106,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>7401</v>
+        <v>1402</v>
       </c>
       <c r="C40" t="n">
-        <v>7882</v>
+        <v>4484.5</v>
       </c>
       <c r="D40" t="n">
-        <v>9503</v>
+        <v>8507</v>
       </c>
       <c r="E40" t="n">
-        <v>572.8528606893746</v>
+        <v>2729.707539279621</v>
       </c>
     </row>
     <row r="41">
@@ -1123,16 +1123,16 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>7401</v>
+        <v>1402</v>
       </c>
       <c r="C41" t="n">
-        <v>56254175.3</v>
+        <v>57805385.9</v>
       </c>
       <c r="D41" t="n">
-        <v>109794673</v>
+        <v>133280818</v>
       </c>
       <c r="E41" t="n">
-        <v>39235683.8861564</v>
+        <v>42984542.70479912</v>
       </c>
     </row>
     <row r="42">
@@ -1140,16 +1140,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>7401</v>
+        <v>902</v>
       </c>
       <c r="C42" t="n">
-        <v>16889550.2</v>
+        <v>18947811.5</v>
       </c>
       <c r="D42" t="n">
-        <v>61251039</v>
+        <v>81355174</v>
       </c>
       <c r="E42" t="n">
-        <v>21545476.43126263</v>
+        <v>29775346.62096409</v>
       </c>
     </row>
     <row r="43">
@@ -1157,16 +1157,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>7401</v>
+        <v>902</v>
       </c>
       <c r="C43" t="n">
-        <v>3909203.8</v>
+        <v>226899</v>
       </c>
       <c r="D43" t="n">
-        <v>33605527</v>
+        <v>2258870</v>
       </c>
       <c r="E43" t="n">
-        <v>10012493.71389626</v>
+        <v>677323.7313822689</v>
       </c>
     </row>
     <row r="44">
@@ -1174,16 +1174,16 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>7401</v>
+        <v>902</v>
       </c>
       <c r="C44" t="n">
-        <v>20444.3</v>
+        <v>1542.4</v>
       </c>
       <c r="D44" t="n">
-        <v>78227</v>
+        <v>6106</v>
       </c>
       <c r="E44" t="n">
-        <v>24394.19180481288</v>
+        <v>1562.705807245881</v>
       </c>
     </row>
     <row r="45">
@@ -1191,16 +1191,16 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>6601</v>
+        <v>501</v>
       </c>
       <c r="C45" t="n">
-        <v>8512</v>
+        <v>872</v>
       </c>
       <c r="D45" t="n">
-        <v>13204</v>
+        <v>1003</v>
       </c>
       <c r="E45" t="n">
-        <v>1973.11464441375</v>
+        <v>127.280006285355</v>
       </c>
     </row>
     <row r="46">
@@ -1208,16 +1208,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2802</v>
+        <v>501</v>
       </c>
       <c r="C46" t="n">
-        <v>7411.6</v>
+        <v>1271.9</v>
       </c>
       <c r="D46" t="n">
-        <v>13204</v>
+        <v>5302</v>
       </c>
       <c r="E46" t="n">
-        <v>2399.072495778316</v>
+        <v>1362.502950455521</v>
       </c>
     </row>
     <row r="47">
@@ -1225,16 +1225,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>2802</v>
+        <v>501</v>
       </c>
       <c r="C47" t="n">
-        <v>5711.3</v>
+        <v>711.6</v>
       </c>
       <c r="D47" t="n">
-        <v>7502</v>
+        <v>902</v>
       </c>
       <c r="E47" t="n">
-        <v>1640.150666859603</v>
+        <v>192.5311403383878</v>
       </c>
     </row>
     <row r="48">
@@ -1242,16 +1242,16 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>2802</v>
+        <v>201</v>
       </c>
       <c r="C48" t="n">
-        <v>4781.4</v>
+        <v>671.2</v>
       </c>
       <c r="D48" t="n">
-        <v>6601</v>
+        <v>2500</v>
       </c>
       <c r="E48" t="n">
-        <v>1706.463079002883</v>
+        <v>640.0721521828614</v>
       </c>
     </row>
     <row r="49">
@@ -1259,16 +1259,16 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>2802</v>
+        <v>201</v>
       </c>
       <c r="C49" t="n">
-        <v>2802</v>
+        <v>491.1</v>
       </c>
       <c r="D49" t="n">
-        <v>2802</v>
+        <v>1600</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>390.6690287186841</v>
       </c>
     </row>
     <row r="50">
@@ -1276,16 +1276,16 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>2802</v>
+        <v>201</v>
       </c>
       <c r="C50" t="n">
-        <v>2932.1</v>
+        <v>411.1</v>
       </c>
       <c r="D50" t="n">
-        <v>3902</v>
+        <v>1600</v>
       </c>
       <c r="E50" t="n">
-        <v>328.8070710918486</v>
+        <v>410.6802771012994</v>
       </c>
     </row>
     <row r="51">
@@ -1293,16 +1293,16 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C51" t="n">
-        <v>3322.3</v>
+        <v>231.2</v>
       </c>
       <c r="D51" t="n">
-        <v>6502</v>
+        <v>502</v>
       </c>
       <c r="E51" t="n">
-        <v>1178.807961459372</v>
+        <v>119.1140629816648</v>
       </c>
     </row>
     <row r="52">
@@ -1310,16 +1310,16 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C52" t="n">
-        <v>2893</v>
+        <v>241.4</v>
       </c>
       <c r="D52" t="n">
-        <v>4303</v>
+        <v>603</v>
       </c>
       <c r="E52" t="n">
-        <v>474.2575249798363</v>
+        <v>163.0596209979651</v>
       </c>
     </row>
     <row r="53">
@@ -1327,16 +1327,16 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C53" t="n">
-        <v>3082.9</v>
+        <v>341.1</v>
       </c>
       <c r="D53" t="n">
-        <v>6502</v>
+        <v>1600</v>
       </c>
       <c r="E53" t="n">
-        <v>1139.7</v>
+        <v>445.1879266107742</v>
       </c>
     </row>
     <row r="54">
@@ -1344,16 +1344,16 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C54" t="n">
-        <v>5184.6</v>
+        <v>620.9</v>
       </c>
       <c r="D54" t="n">
-        <v>27318</v>
+        <v>1701</v>
       </c>
       <c r="E54" t="n">
-        <v>7378.043374770848</v>
+        <v>695.2726731290393</v>
       </c>
     </row>
     <row r="55">
@@ -1361,16 +1361,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C55" t="n">
-        <v>2743.2</v>
+        <v>2502.2</v>
       </c>
       <c r="D55" t="n">
-        <v>2904</v>
+        <v>20509</v>
       </c>
       <c r="E55" t="n">
-        <v>80.40000000000001</v>
+        <v>6030.726801970058</v>
       </c>
     </row>
     <row r="56">
@@ -1378,16 +1378,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C56" t="n">
-        <v>2723.1</v>
+        <v>151.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2904</v>
+        <v>302</v>
       </c>
       <c r="E56" t="n">
-        <v>60.3</v>
+        <v>67.45524442176458</v>
       </c>
     </row>
     <row r="57">
@@ -1395,16 +1395,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C57" t="n">
-        <v>2703</v>
+        <v>211.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2703</v>
+        <v>602</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>176.1652917007207</v>
       </c>
     </row>
     <row r="58">
@@ -1412,16 +1412,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C58" t="n">
-        <v>2743</v>
+        <v>511.6</v>
       </c>
       <c r="D58" t="n">
-        <v>3103</v>
+        <v>2904</v>
       </c>
       <c r="E58" t="n">
-        <v>120</v>
+        <v>811.3253601361172</v>
       </c>
     </row>
     <row r="59">
@@ -1429,16 +1429,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C59" t="n">
-        <v>2703</v>
+        <v>161.2</v>
       </c>
       <c r="D59" t="n">
-        <v>2703</v>
+        <v>502</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>128.4373777371681</v>
       </c>
     </row>
     <row r="60">
@@ -1446,16 +1446,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C60" t="n">
-        <v>2703</v>
+        <v>181.3</v>
       </c>
       <c r="D60" t="n">
-        <v>2703</v>
+        <v>502</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>133.0872270355048</v>
       </c>
     </row>
     <row r="61">
@@ -1463,16 +1463,16 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C61" t="n">
-        <v>54747891</v>
+        <v>52805880.6</v>
       </c>
       <c r="D61" t="n">
-        <v>137233341</v>
+        <v>132859202</v>
       </c>
       <c r="E61" t="n">
-        <v>44888978.51740735</v>
+        <v>47681057.65905596</v>
       </c>
     </row>
     <row r="62">
@@ -1480,16 +1480,16 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C62" t="n">
-        <v>21094635.7</v>
+        <v>14273522.2</v>
       </c>
       <c r="D62" t="n">
-        <v>57477271</v>
+        <v>80725342</v>
       </c>
       <c r="E62" t="n">
-        <v>17783091.55009501</v>
+        <v>23409334.24302593</v>
       </c>
     </row>
     <row r="63">
@@ -1497,16 +1497,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C63" t="n">
-        <v>6462744.7</v>
+        <v>5725159.7</v>
       </c>
       <c r="D63" t="n">
-        <v>26601495</v>
+        <v>16264742</v>
       </c>
       <c r="E63" t="n">
-        <v>8009831.168195196</v>
+        <v>6891227.83820946</v>
       </c>
     </row>
     <row r="64">
@@ -1514,16 +1514,16 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C64" t="n">
-        <v>2117942.9</v>
+        <v>131743.8</v>
       </c>
       <c r="D64" t="n">
-        <v>7215239</v>
+        <v>659765</v>
       </c>
       <c r="E64" t="n">
-        <v>2956503.580392807</v>
+        <v>263186.8989147446</v>
       </c>
     </row>
     <row r="65">
@@ -1531,16 +1531,16 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C65" t="n">
-        <v>589873.8</v>
+        <v>231.1</v>
       </c>
       <c r="D65" t="n">
-        <v>5220547</v>
+        <v>1002</v>
       </c>
       <c r="E65" t="n">
-        <v>1555819.355037904</v>
+        <v>283.29152828844</v>
       </c>
     </row>
     <row r="66">
@@ -1548,16 +1548,16 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>2703</v>
+        <v>101</v>
       </c>
       <c r="C66" t="n">
-        <v>2703</v>
+        <v>111.2</v>
       </c>
       <c r="D66" t="n">
-        <v>2703</v>
+        <v>203</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="67">
@@ -1565,16 +1565,16 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>1803</v>
+        <v>101</v>
       </c>
       <c r="C67" t="n">
-        <v>2583.1</v>
+        <v>211.1</v>
       </c>
       <c r="D67" t="n">
-        <v>3304</v>
+        <v>1102</v>
       </c>
       <c r="E67" t="n">
-        <v>428.653811367635</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="68">
@@ -1582,16 +1582,16 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>1803</v>
+        <v>101</v>
       </c>
       <c r="C68" t="n">
-        <v>2363.1</v>
+        <v>141</v>
       </c>
       <c r="D68" t="n">
-        <v>2703</v>
+        <v>501</v>
       </c>
       <c r="E68" t="n">
-        <v>419.9143841308607</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69">
@@ -1599,16 +1599,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>1803</v>
+        <v>101</v>
       </c>
       <c r="C69" t="n">
-        <v>1913.1</v>
+        <v>621.3</v>
       </c>
       <c r="D69" t="n">
-        <v>2703</v>
+        <v>5304</v>
       </c>
       <c r="E69" t="n">
-        <v>270.0334979220171</v>
+        <v>1560.9</v>
       </c>
     </row>
     <row r="70">
@@ -1616,16 +1616,16 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>1103</v>
+        <v>101</v>
       </c>
       <c r="C70" t="n">
-        <v>2003</v>
+        <v>881.6</v>
       </c>
       <c r="D70" t="n">
-        <v>5002</v>
+        <v>7305</v>
       </c>
       <c r="E70" t="n">
-        <v>1041.825417236496</v>
+        <v>2144.88821153924</v>
       </c>
     </row>
     <row r="71">
@@ -1633,16 +1633,16 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>1103</v>
+        <v>101</v>
       </c>
       <c r="C71" t="n">
-        <v>1453</v>
+        <v>1682.1</v>
       </c>
       <c r="D71" t="n">
-        <v>1803</v>
+        <v>15309</v>
       </c>
       <c r="E71" t="n">
-        <v>350</v>
+        <v>4543.849633295538</v>
       </c>
     </row>
     <row r="72">
@@ -1650,16 +1650,16 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>1103</v>
+        <v>101</v>
       </c>
       <c r="C72" t="n">
-        <v>1182.9</v>
+        <v>641.6</v>
       </c>
       <c r="D72" t="n">
-        <v>1803</v>
+        <v>5406</v>
       </c>
       <c r="E72" t="n">
-        <v>208.7967672163532</v>
+        <v>1588.418786088857</v>
       </c>
     </row>
     <row r="73">
@@ -1667,16 +1667,16 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>1103</v>
+        <v>101</v>
       </c>
       <c r="C73" t="n">
-        <v>1112.9</v>
+        <v>1701.7</v>
       </c>
       <c r="D73" t="n">
-        <v>1202</v>
+        <v>15309</v>
       </c>
       <c r="E73" t="n">
-        <v>29.7</v>
+        <v>4542.017834619322</v>
       </c>
     </row>
     <row r="74">
@@ -1684,16 +1684,16 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>1103</v>
+        <v>101</v>
       </c>
       <c r="C74" t="n">
-        <v>1123.1</v>
+        <v>701.8</v>
       </c>
       <c r="D74" t="n">
-        <v>1304</v>
+        <v>2904</v>
       </c>
       <c r="E74" t="n">
-        <v>60.3</v>
+        <v>1103.848431624559</v>
       </c>
     </row>
     <row r="75">
@@ -1701,16 +1701,16 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="C75" t="n">
-        <v>1422.9</v>
+        <v>161.4</v>
       </c>
       <c r="D75" t="n">
-        <v>3702</v>
+        <v>503</v>
       </c>
       <c r="E75" t="n">
-        <v>937.6268394196062</v>
+        <v>120.6334945195571</v>
       </c>
     </row>
     <row r="76">
@@ -1718,16 +1718,16 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="C76" t="n">
-        <v>923.1</v>
+        <v>151.2</v>
       </c>
       <c r="D76" t="n">
-        <v>1304</v>
+        <v>502</v>
       </c>
       <c r="E76" t="n">
-        <v>267.7239062915376</v>
+        <v>120.748333321831</v>
       </c>
     </row>
     <row r="77">
@@ -1735,16 +1735,16 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="C77" t="n">
-        <v>802.9</v>
+        <v>121.1</v>
       </c>
       <c r="D77" t="n">
-        <v>2602</v>
+        <v>302</v>
       </c>
       <c r="E77" t="n">
-        <v>599.6999999999999</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="78">
@@ -1752,16 +1752,16 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>923</v>
+        <v>241.2</v>
       </c>
       <c r="D78" t="n">
-        <v>3803</v>
+        <v>900</v>
       </c>
       <c r="E78" t="n">
-        <v>960</v>
+        <v>232.9900427056916</v>
       </c>
     </row>
     <row r="79">
@@ -1769,16 +1769,16 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="C79" t="n">
-        <v>832.9</v>
+        <v>651.6</v>
       </c>
       <c r="D79" t="n">
-        <v>2602</v>
+        <v>5305</v>
       </c>
       <c r="E79" t="n">
-        <v>719.5457525411431</v>
+        <v>1552.437257991446</v>
       </c>
     </row>
     <row r="80">
@@ -1786,16 +1786,16 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C80" t="n">
-        <v>403.1</v>
+        <v>871.8</v>
       </c>
       <c r="D80" t="n">
-        <v>904</v>
+        <v>5406</v>
       </c>
       <c r="E80" t="n">
-        <v>214.7093151216314</v>
+        <v>1560.977309252124</v>
       </c>
     </row>
     <row r="81">
@@ -1803,16 +1803,16 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C81" t="n">
-        <v>90182558.5</v>
+        <v>47188306.7</v>
       </c>
       <c r="D81" t="n">
-        <v>216550378</v>
+        <v>128627558</v>
       </c>
       <c r="E81" t="n">
-        <v>67332805.70754844</v>
+        <v>45178035.24571519</v>
       </c>
     </row>
     <row r="82">
@@ -1820,16 +1820,16 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C82" t="n">
-        <v>48437977.3</v>
+        <v>8077428.7</v>
       </c>
       <c r="D82" t="n">
-        <v>116237363</v>
+        <v>28937294</v>
       </c>
       <c r="E82" t="n">
-        <v>29610945.80457864</v>
+        <v>10589635.11341597</v>
       </c>
     </row>
     <row r="83">
@@ -1837,16 +1837,16 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C83" t="n">
-        <v>19741009.9</v>
+        <v>1000730.8</v>
       </c>
       <c r="D83" t="n">
-        <v>62317945</v>
+        <v>5337197</v>
       </c>
       <c r="E83" t="n">
-        <v>18144044.30445558</v>
+        <v>1673612.3172484</v>
       </c>
     </row>
     <row r="84">
@@ -1854,16 +1854,16 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C84" t="n">
-        <v>9125457</v>
+        <v>351</v>
       </c>
       <c r="D84" t="n">
-        <v>32198258</v>
+        <v>1001</v>
       </c>
       <c r="E84" t="n">
-        <v>11284277.54782894</v>
+        <v>338.2605504636921</v>
       </c>
     </row>
     <row r="85">
@@ -1871,16 +1871,16 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C85" t="n">
-        <v>94501.2</v>
+        <v>151</v>
       </c>
       <c r="D85" t="n">
-        <v>925684</v>
+        <v>501</v>
       </c>
       <c r="E85" t="n">
-        <v>277072.6176527735</v>
+        <v>120.415945787923</v>
       </c>
     </row>
     <row r="86">
@@ -1888,16 +1888,16 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C86" t="n">
-        <v>642.9</v>
+        <v>121.1</v>
       </c>
       <c r="D86" t="n">
-        <v>1803</v>
+        <v>302</v>
       </c>
       <c r="E86" t="n">
-        <v>631.1323870631264</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="87">
@@ -1905,16 +1905,16 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C87" t="n">
-        <v>263.1</v>
+        <v>101</v>
       </c>
       <c r="D87" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="E87" t="n">
-        <v>128.172110850996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1922,16 +1922,16 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C88" t="n">
-        <v>223.1</v>
+        <v>260.8</v>
       </c>
       <c r="D88" t="n">
-        <v>404</v>
+        <v>900</v>
       </c>
       <c r="E88" t="n">
-        <v>60.3</v>
+        <v>319.6</v>
       </c>
     </row>
     <row r="89">
@@ -1939,16 +1939,16 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C89" t="n">
-        <v>553.3</v>
+        <v>171.4</v>
       </c>
       <c r="D89" t="n">
-        <v>3006</v>
+        <v>302</v>
       </c>
       <c r="E89" t="n">
-        <v>836.7024620496823</v>
+        <v>64.37577184003311</v>
       </c>
     </row>
     <row r="90">
@@ -1956,16 +1956,16 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C90" t="n">
-        <v>282.9</v>
+        <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="E90" t="n">
-        <v>239.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1973,16 +1973,16 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C91" t="n">
-        <v>233.1</v>
+        <v>121.1</v>
       </c>
       <c r="D91" t="n">
-        <v>404</v>
+        <v>302</v>
       </c>
       <c r="E91" t="n">
-        <v>64.29688950485863</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="92">
@@ -1990,16 +1990,16 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C92" t="n">
-        <v>253</v>
+        <v>191.2</v>
       </c>
       <c r="D92" t="n">
-        <v>603</v>
+        <v>502</v>
       </c>
       <c r="E92" t="n">
-        <v>120.415945787923</v>
+        <v>158.1902651872106</v>
       </c>
     </row>
     <row r="93">
@@ -2007,16 +2007,16 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C93" t="n">
-        <v>203</v>
+        <v>111</v>
       </c>
       <c r="D93" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
@@ -2024,16 +2024,16 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C94" t="n">
-        <v>533.4</v>
+        <v>311.3</v>
       </c>
       <c r="D94" t="n">
-        <v>3006</v>
+        <v>2103</v>
       </c>
       <c r="E94" t="n">
-        <v>830.3955924738522</v>
+        <v>597.9919815515924</v>
       </c>
     </row>
     <row r="95">
@@ -2041,16 +2041,16 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C95" t="n">
-        <v>243</v>
+        <v>191.1</v>
       </c>
       <c r="D95" t="n">
-        <v>603</v>
+        <v>1002</v>
       </c>
       <c r="E95" t="n">
-        <v>120</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="96">
@@ -2058,16 +2058,16 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C96" t="n">
-        <v>212.9</v>
+        <v>201.1</v>
       </c>
       <c r="D96" t="n">
-        <v>302</v>
+        <v>1102</v>
       </c>
       <c r="E96" t="n">
-        <v>29.7</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="97">
@@ -2075,16 +2075,16 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C97" t="n">
-        <v>223.1</v>
+        <v>101</v>
       </c>
       <c r="D97" t="n">
-        <v>404</v>
+        <v>101</v>
       </c>
       <c r="E97" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2092,16 +2092,16 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>203</v>
+        <v>141.1</v>
       </c>
       <c r="D98" t="n">
-        <v>203</v>
+        <v>502</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="99">
@@ -2109,16 +2109,16 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C99" t="n">
-        <v>643.3</v>
+        <v>461.3</v>
       </c>
       <c r="D99" t="n">
-        <v>3006</v>
+        <v>1902</v>
       </c>
       <c r="E99" t="n">
-        <v>920.7696834713879</v>
+        <v>542.7563081162668</v>
       </c>
     </row>
     <row r="100">
@@ -2126,16 +2126,16 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C100" t="n">
-        <v>203</v>
+        <v>2752.1</v>
       </c>
       <c r="D100" t="n">
-        <v>203</v>
+        <v>24309</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>7205.265816748193</v>
       </c>
     </row>
     <row r="101">
@@ -2143,16 +2143,16 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C101" t="n">
-        <v>74945489.59999999</v>
+        <v>34878216.1</v>
       </c>
       <c r="D101" t="n">
-        <v>174658237</v>
+        <v>81990083</v>
       </c>
       <c r="E101" t="n">
-        <v>47532667.11418112</v>
+        <v>27268291.33389294</v>
       </c>
     </row>
     <row r="102">
@@ -2160,16 +2160,16 @@
         <v>0</v>
       </c>
       <c r="B102" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>29086822.2</v>
+        <v>9616366.1</v>
       </c>
       <c r="D102" t="n">
-        <v>93031515</v>
+        <v>32988231</v>
       </c>
       <c r="E102" t="n">
-        <v>35506954.50902899</v>
+        <v>10326588.79627454</v>
       </c>
     </row>
     <row r="103">
@@ -2177,16 +2177,16 @@
         <v>1</v>
       </c>
       <c r="B103" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C103" t="n">
-        <v>573.6</v>
+        <v>48740.4</v>
       </c>
       <c r="D103" t="n">
-        <v>3407</v>
+        <v>241146</v>
       </c>
       <c r="E103" t="n">
-        <v>949.9039109299423</v>
+        <v>96204.32720642039</v>
       </c>
     </row>
     <row r="104">
@@ -2194,16 +2194,16 @@
         <v>2</v>
       </c>
       <c r="B104" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C104" t="n">
-        <v>233</v>
+        <v>451.5</v>
       </c>
       <c r="D104" t="n">
-        <v>404</v>
+        <v>1701</v>
       </c>
       <c r="E104" t="n">
-        <v>64.18878406700037</v>
+        <v>467.1300140217925</v>
       </c>
     </row>
     <row r="105">
@@ -2211,16 +2211,16 @@
         <v>3</v>
       </c>
       <c r="B105" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C105" t="n">
-        <v>282.9</v>
+        <v>261.8</v>
       </c>
       <c r="D105" t="n">
-        <v>1002</v>
+        <v>603</v>
       </c>
       <c r="E105" t="n">
-        <v>239.7</v>
+        <v>186.1842098567975</v>
       </c>
     </row>
     <row r="106">
@@ -2228,16 +2228,16 @@
         <v>4</v>
       </c>
       <c r="B106" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C106" t="n">
-        <v>243.1</v>
+        <v>341.3</v>
       </c>
       <c r="D106" t="n">
-        <v>404</v>
+        <v>1701</v>
       </c>
       <c r="E106" t="n">
-        <v>66.57394385193054</v>
+        <v>477.9290846977196</v>
       </c>
     </row>
     <row r="107">
@@ -2245,16 +2245,16 @@
         <v>5</v>
       </c>
       <c r="B107" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C107" t="n">
-        <v>213</v>
+        <v>681.5</v>
       </c>
       <c r="D107" t="n">
-        <v>303</v>
+        <v>1803</v>
       </c>
       <c r="E107" t="n">
-        <v>30</v>
+        <v>692.9075335136716</v>
       </c>
     </row>
     <row r="108">
@@ -2262,16 +2262,16 @@
         <v>6</v>
       </c>
       <c r="B108" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C108" t="n">
-        <v>282.9</v>
+        <v>301.1</v>
       </c>
       <c r="D108" t="n">
-        <v>1002</v>
+        <v>1101</v>
       </c>
       <c r="E108" t="n">
-        <v>239.7</v>
+        <v>354.7397496757306</v>
       </c>
     </row>
     <row r="109">
@@ -2279,16 +2279,16 @@
         <v>7</v>
       </c>
       <c r="B109" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C109" t="n">
-        <v>353</v>
+        <v>131.3</v>
       </c>
       <c r="D109" t="n">
-        <v>1002</v>
+        <v>202</v>
       </c>
       <c r="E109" t="n">
-        <v>280.1074793717583</v>
+        <v>46.28401451905398</v>
       </c>
     </row>
     <row r="110">
@@ -2296,16 +2296,16 @@
         <v>8</v>
       </c>
       <c r="B110" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="C110" t="n">
-        <v>263.1</v>
+        <v>380.9</v>
       </c>
       <c r="D110" t="n">
-        <v>603</v>
+        <v>2601</v>
       </c>
       <c r="E110" t="n">
-        <v>128.172110850996</v>
+        <v>745.3831833359268</v>
       </c>
     </row>
     <row r="111">
@@ -2313,16 +2313,16 @@
         <v>9</v>
       </c>
       <c r="B111" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C111" t="n">
-        <v>682.7</v>
+        <v>141.1</v>
       </c>
       <c r="D111" t="n">
-        <v>1803</v>
+        <v>502</v>
       </c>
       <c r="E111" t="n">
-        <v>733.1904322889109</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="112">
@@ -2330,16 +2330,16 @@
         <v>10</v>
       </c>
       <c r="B112" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C112" t="n">
-        <v>463</v>
+        <v>521.6</v>
       </c>
       <c r="D112" t="n">
-        <v>1802</v>
+        <v>2904</v>
       </c>
       <c r="E112" t="n">
-        <v>479.8337211993338</v>
+        <v>845.5985099324621</v>
       </c>
     </row>
     <row r="113">
@@ -2347,16 +2347,16 @@
         <v>11</v>
       </c>
       <c r="B113" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C113" t="n">
-        <v>232.5</v>
+        <v>221.3</v>
       </c>
       <c r="D113" t="n">
-        <v>303</v>
+        <v>702</v>
       </c>
       <c r="E113" t="n">
-        <v>45.93745748297352</v>
+        <v>199.3695312729606</v>
       </c>
     </row>
     <row r="114">
@@ -2364,16 +2364,16 @@
         <v>12</v>
       </c>
       <c r="B114" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C114" t="n">
-        <v>482.2</v>
+        <v>571.5</v>
       </c>
       <c r="D114" t="n">
-        <v>1803</v>
+        <v>2904</v>
       </c>
       <c r="E114" t="n">
-        <v>507.6695381840435</v>
+        <v>863.533931006767</v>
       </c>
     </row>
     <row r="115">
@@ -2381,16 +2381,16 @@
         <v>13</v>
       </c>
       <c r="B115" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C115" t="n">
-        <v>332.2</v>
+        <v>241.2</v>
       </c>
       <c r="D115" t="n">
-        <v>1102</v>
+        <v>1002</v>
       </c>
       <c r="E115" t="n">
-        <v>283.0691788238345</v>
+        <v>280.2573103417643</v>
       </c>
     </row>
     <row r="116">
@@ -2398,16 +2398,16 @@
         <v>14</v>
       </c>
       <c r="B116" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C116" t="n">
-        <v>212</v>
+        <v>781.4</v>
       </c>
       <c r="D116" t="n">
-        <v>302</v>
+        <v>5305</v>
       </c>
       <c r="E116" t="n">
-        <v>30</v>
+        <v>1581.523771557039</v>
       </c>
     </row>
     <row r="117">
@@ -2415,16 +2415,16 @@
         <v>15</v>
       </c>
       <c r="B117" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C117" t="n">
-        <v>292.1</v>
+        <v>361.1</v>
       </c>
       <c r="D117" t="n">
-        <v>703</v>
+        <v>1701</v>
       </c>
       <c r="E117" t="n">
-        <v>181.6097189029266</v>
+        <v>537.1667245837181</v>
       </c>
     </row>
     <row r="118">
@@ -2432,16 +2432,16 @@
         <v>16</v>
       </c>
       <c r="B118" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C118" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D118" t="n">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="E118" t="n">
-        <v>240</v>
+        <v>362.8225461572089</v>
       </c>
     </row>
     <row r="119">
@@ -2449,16 +2449,16 @@
         <v>17</v>
       </c>
       <c r="B119" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C119" t="n">
-        <v>1722.8</v>
+        <v>261</v>
       </c>
       <c r="D119" t="n">
-        <v>15410</v>
+        <v>1701</v>
       </c>
       <c r="E119" t="n">
-        <v>4562.4</v>
+        <v>480</v>
       </c>
     </row>
     <row r="120">
@@ -2466,16 +2466,16 @@
         <v>18</v>
       </c>
       <c r="B120" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C120" t="n">
-        <v>242.1</v>
+        <v>101</v>
       </c>
       <c r="D120" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="E120" t="n">
-        <v>120.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2483,16 +2483,16 @@
         <v>19</v>
       </c>
       <c r="B121" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C121" t="n">
-        <v>71423437.40000001</v>
+        <v>53369790.5</v>
       </c>
       <c r="D121" t="n">
-        <v>210891262</v>
+        <v>175524970</v>
       </c>
       <c r="E121" t="n">
-        <v>66896489.80107365</v>
+        <v>63696698.2484167</v>
       </c>
     </row>
     <row r="122">
@@ -2500,16 +2500,16 @@
         <v>20</v>
       </c>
       <c r="B122" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C122" t="n">
-        <v>6466245.8</v>
+        <v>13999787.4</v>
       </c>
       <c r="D122" t="n">
-        <v>19379758</v>
+        <v>63286809</v>
       </c>
       <c r="E122" t="n">
-        <v>7173100.584242978</v>
+        <v>23574579.4388858</v>
       </c>
     </row>
     <row r="123">
@@ -2517,16 +2517,16 @@
         <v>21</v>
       </c>
       <c r="B123" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C123" t="n">
-        <v>652663.4</v>
+        <v>7582520.4</v>
       </c>
       <c r="D123" t="n">
-        <v>6514412</v>
+        <v>53354871</v>
       </c>
       <c r="E123" t="n">
-        <v>1953917.351292434</v>
+        <v>15716719.27814065</v>
       </c>
     </row>
     <row r="124">
@@ -2534,16 +2534,16 @@
         <v>22</v>
       </c>
       <c r="B124" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C124" t="n">
-        <v>492.2</v>
+        <v>6022.8</v>
       </c>
       <c r="D124" t="n">
-        <v>1802</v>
+        <v>57717</v>
       </c>
       <c r="E124" t="n">
-        <v>563.048985435548</v>
+        <v>17233.99926192409</v>
       </c>
     </row>
     <row r="125">
@@ -2551,16 +2551,16 @@
         <v>23</v>
       </c>
       <c r="B125" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C125" t="n">
-        <v>242.3</v>
+        <v>261.2</v>
       </c>
       <c r="D125" t="n">
-        <v>603</v>
+        <v>1102</v>
       </c>
       <c r="E125" t="n">
-        <v>120.233980221899</v>
+        <v>304.230438976773</v>
       </c>
     </row>
     <row r="126">
@@ -2568,16 +2568,16 @@
         <v>24</v>
       </c>
       <c r="B126" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C126" t="n">
-        <v>242.2</v>
+        <v>101</v>
       </c>
       <c r="D126" t="n">
-        <v>603</v>
+        <v>101</v>
       </c>
       <c r="E126" t="n">
-        <v>120.267036215249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2585,16 +2585,16 @@
         <v>25</v>
       </c>
       <c r="B127" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C127" t="n">
-        <v>202</v>
+        <v>191.4</v>
       </c>
       <c r="D127" t="n">
-        <v>202</v>
+        <v>502</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>130.415643233471</v>
       </c>
     </row>
     <row r="128">
@@ -2602,16 +2602,16 @@
         <v>26</v>
       </c>
       <c r="B128" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="C128" t="n">
-        <v>441.9</v>
+        <v>761.6</v>
       </c>
       <c r="D128" t="n">
-        <v>1802</v>
+        <v>5305</v>
       </c>
       <c r="E128" t="n">
-        <v>512.1406935598849</v>
+        <v>1534.186963834591</v>
       </c>
     </row>
     <row r="129">
@@ -2622,13 +2622,13 @@
         <v>101</v>
       </c>
       <c r="C129" t="n">
-        <v>281.8</v>
+        <v>131.2</v>
       </c>
       <c r="D129" t="n">
-        <v>1001</v>
+        <v>302</v>
       </c>
       <c r="E129" t="n">
-        <v>243.9101473903864</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="130">
@@ -2639,13 +2639,13 @@
         <v>101</v>
       </c>
       <c r="C130" t="n">
-        <v>181.4</v>
+        <v>261.1</v>
       </c>
       <c r="D130" t="n">
-        <v>501</v>
+        <v>1702</v>
       </c>
       <c r="E130" t="n">
-        <v>116.6886455487422</v>
+        <v>480.3</v>
       </c>
     </row>
     <row r="131">
@@ -2656,13 +2656,13 @@
         <v>101</v>
       </c>
       <c r="C131" t="n">
-        <v>191.1</v>
+        <v>191.2</v>
       </c>
       <c r="D131" t="n">
-        <v>900</v>
+        <v>602</v>
       </c>
       <c r="E131" t="n">
-        <v>238.2487985279254</v>
+        <v>181.7805270099083</v>
       </c>
     </row>
     <row r="132">
@@ -2673,13 +2673,13 @@
         <v>101</v>
       </c>
       <c r="C132" t="n">
-        <v>151</v>
+        <v>131.2</v>
       </c>
       <c r="D132" t="n">
-        <v>501</v>
+        <v>302</v>
       </c>
       <c r="E132" t="n">
-        <v>120.415945787923</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="133">
@@ -2690,13 +2690,13 @@
         <v>101</v>
       </c>
       <c r="C133" t="n">
-        <v>341.3</v>
+        <v>401.3</v>
       </c>
       <c r="D133" t="n">
-        <v>1101</v>
+        <v>2904</v>
       </c>
       <c r="E133" t="n">
-        <v>385.5339284680403</v>
+        <v>835.1651393586778</v>
       </c>
     </row>
     <row r="134">
@@ -2707,13 +2707,13 @@
         <v>101</v>
       </c>
       <c r="C134" t="n">
-        <v>521.6</v>
+        <v>151.3</v>
       </c>
       <c r="D134" t="n">
-        <v>2904</v>
+        <v>302</v>
       </c>
       <c r="E134" t="n">
-        <v>845.6695808647726</v>
+        <v>67.45524442176458</v>
       </c>
     </row>
     <row r="135">
@@ -2724,13 +2724,13 @@
         <v>101</v>
       </c>
       <c r="C135" t="n">
-        <v>421.4</v>
+        <v>401.4</v>
       </c>
       <c r="D135" t="n">
-        <v>2904</v>
+        <v>3005</v>
       </c>
       <c r="E135" t="n">
-        <v>836.124894976821</v>
+        <v>868.3786270976503</v>
       </c>
     </row>
     <row r="136">
@@ -2741,13 +2741,13 @@
         <v>101</v>
       </c>
       <c r="C136" t="n">
-        <v>191.1</v>
+        <v>211.1</v>
       </c>
       <c r="D136" t="n">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="E136" t="n">
-        <v>270.3</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="137">
@@ -2758,13 +2758,13 @@
         <v>101</v>
       </c>
       <c r="C137" t="n">
-        <v>221.3</v>
+        <v>111</v>
       </c>
       <c r="D137" t="n">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="E137" t="n">
-        <v>183.7612853677292</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
@@ -2775,13 +2775,13 @@
         <v>101</v>
       </c>
       <c r="C138" t="n">
-        <v>131.1</v>
+        <v>101</v>
       </c>
       <c r="D138" t="n">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="E138" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -2792,13 +2792,13 @@
         <v>101</v>
       </c>
       <c r="C139" t="n">
-        <v>131.2</v>
+        <v>1912.1</v>
       </c>
       <c r="D139" t="n">
-        <v>302</v>
+        <v>15309</v>
       </c>
       <c r="E139" t="n">
-        <v>64.40621088062858</v>
+        <v>4542.568006095231</v>
       </c>
     </row>
     <row r="140">
@@ -2809,13 +2809,13 @@
         <v>101</v>
       </c>
       <c r="C140" t="n">
-        <v>111.1</v>
+        <v>221.1</v>
       </c>
       <c r="D140" t="n">
-        <v>202</v>
+        <v>1001</v>
       </c>
       <c r="E140" t="n">
-        <v>30.3</v>
+        <v>267.6118270928996</v>
       </c>
     </row>
     <row r="141">
@@ -2826,13 +2826,13 @@
         <v>101</v>
       </c>
       <c r="C141" t="n">
-        <v>55617023.4</v>
+        <v>43581556.6</v>
       </c>
       <c r="D141" t="n">
-        <v>162425958</v>
+        <v>129146118</v>
       </c>
       <c r="E141" t="n">
-        <v>44967821.48040168</v>
+        <v>41760276.72642928</v>
       </c>
     </row>
     <row r="142">
@@ -2843,13 +2843,13 @@
         <v>101</v>
       </c>
       <c r="C142" t="n">
-        <v>22430661</v>
+        <v>15982487.6</v>
       </c>
       <c r="D142" t="n">
-        <v>52999177</v>
+        <v>73262954</v>
       </c>
       <c r="E142" t="n">
-        <v>18262260.29012502</v>
+        <v>23787452.837977</v>
       </c>
     </row>
     <row r="143">
@@ -2860,13 +2860,13 @@
         <v>101</v>
       </c>
       <c r="C143" t="n">
-        <v>14589542.7</v>
+        <v>1234945.1</v>
       </c>
       <c r="D143" t="n">
-        <v>35479073</v>
+        <v>5068301</v>
       </c>
       <c r="E143" t="n">
-        <v>15381685.05422277</v>
+        <v>1910334.735701492</v>
       </c>
     </row>
     <row r="144">
@@ -2877,13 +2877,13 @@
         <v>101</v>
       </c>
       <c r="C144" t="n">
-        <v>4093955.6</v>
+        <v>4591.3</v>
       </c>
       <c r="D144" t="n">
-        <v>27927284</v>
+        <v>44302</v>
       </c>
       <c r="E144" t="n">
-        <v>8501904.06912994</v>
+        <v>13237.48866703953</v>
       </c>
     </row>
     <row r="145">
@@ -2894,13 +2894,13 @@
         <v>101</v>
       </c>
       <c r="C145" t="n">
-        <v>501.2</v>
+        <v>281.4</v>
       </c>
       <c r="D145" t="n">
-        <v>1902</v>
+        <v>1101</v>
       </c>
       <c r="E145" t="n">
-        <v>586.788173023281</v>
+        <v>285.6505557495032</v>
       </c>
     </row>
     <row r="146">
@@ -2911,13 +2911,13 @@
         <v>101</v>
       </c>
       <c r="C146" t="n">
-        <v>491.4</v>
+        <v>151.3</v>
       </c>
       <c r="D146" t="n">
-        <v>2103</v>
+        <v>302</v>
       </c>
       <c r="E146" t="n">
-        <v>713.9666939010531</v>
+        <v>81.05683191440436</v>
       </c>
     </row>
     <row r="147">
@@ -2928,13 +2928,13 @@
         <v>101</v>
       </c>
       <c r="C147" t="n">
-        <v>531.4</v>
+        <v>661.1</v>
       </c>
       <c r="D147" t="n">
-        <v>2904</v>
+        <v>1701</v>
       </c>
       <c r="E147" t="n">
-        <v>858.8695127899232</v>
+        <v>608.611772807592</v>
       </c>
     </row>
     <row r="148">
@@ -2945,13 +2945,13 @@
         <v>101</v>
       </c>
       <c r="C148" t="n">
-        <v>151.1</v>
+        <v>260.9</v>
       </c>
       <c r="D148" t="n">
-        <v>502</v>
+        <v>900</v>
       </c>
       <c r="E148" t="n">
-        <v>120.7066278213421</v>
+        <v>257.4336613576398</v>
       </c>
     </row>
     <row r="149">
@@ -2962,13 +2962,13 @@
         <v>101</v>
       </c>
       <c r="C149" t="n">
-        <v>361.2</v>
+        <v>151.1</v>
       </c>
       <c r="D149" t="n">
-        <v>1701</v>
+        <v>602</v>
       </c>
       <c r="E149" t="n">
-        <v>473.7258278793758</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="150">
@@ -2979,13 +2979,13 @@
         <v>101</v>
       </c>
       <c r="C150" t="n">
-        <v>181.3</v>
+        <v>401.4</v>
       </c>
       <c r="D150" t="n">
-        <v>503</v>
+        <v>1102</v>
       </c>
       <c r="E150" t="n">
-        <v>160.6001556661761</v>
+        <v>419.9526639991703</v>
       </c>
     </row>
     <row r="151">
@@ -2996,13 +2996,13 @@
         <v>101</v>
       </c>
       <c r="C151" t="n">
-        <v>301.1</v>
+        <v>1602.2</v>
       </c>
       <c r="D151" t="n">
-        <v>1202</v>
+        <v>7005</v>
       </c>
       <c r="E151" t="n">
-        <v>402.7158924105181</v>
+        <v>2480.411893214512</v>
       </c>
     </row>
     <row r="152">
@@ -3013,13 +3013,13 @@
         <v>101</v>
       </c>
       <c r="C152" t="n">
-        <v>211.4</v>
+        <v>381.3</v>
       </c>
       <c r="D152" t="n">
-        <v>502</v>
+        <v>2904</v>
       </c>
       <c r="E152" t="n">
-        <v>145.0249633683802</v>
+        <v>840.9</v>
       </c>
     </row>
     <row r="153">
@@ -3030,13 +3030,13 @@
         <v>101</v>
       </c>
       <c r="C153" t="n">
-        <v>721.8</v>
+        <v>151.2</v>
       </c>
       <c r="D153" t="n">
-        <v>3105</v>
+        <v>502</v>
       </c>
       <c r="E153" t="n">
-        <v>1148.377098343571</v>
+        <v>120.748333321831</v>
       </c>
     </row>
     <row r="154">
@@ -3047,13 +3047,13 @@
         <v>101</v>
       </c>
       <c r="C154" t="n">
-        <v>381.3</v>
+        <v>111.1</v>
       </c>
       <c r="D154" t="n">
-        <v>2904</v>
+        <v>202</v>
       </c>
       <c r="E154" t="n">
-        <v>840.8999999999999</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="155">
@@ -3064,13 +3064,13 @@
         <v>101</v>
       </c>
       <c r="C155" t="n">
-        <v>180.9</v>
+        <v>111</v>
       </c>
       <c r="D155" t="n">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E155" t="n">
-        <v>239.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156">
@@ -3081,13 +3081,13 @@
         <v>101</v>
       </c>
       <c r="C156" t="n">
-        <v>151.1</v>
+        <v>250.9</v>
       </c>
       <c r="D156" t="n">
-        <v>502</v>
+        <v>1600</v>
       </c>
       <c r="E156" t="n">
-        <v>120.7066278213421</v>
+        <v>449.7</v>
       </c>
     </row>
     <row r="157">
@@ -3098,13 +3098,13 @@
         <v>101</v>
       </c>
       <c r="C157" t="n">
-        <v>331.1</v>
+        <v>101</v>
       </c>
       <c r="D157" t="n">
-        <v>900</v>
+        <v>101</v>
       </c>
       <c r="E157" t="n">
-        <v>309.6360605614275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -3115,13 +3115,13 @@
         <v>101</v>
       </c>
       <c r="C158" t="n">
-        <v>161.1</v>
+        <v>281.1</v>
       </c>
       <c r="D158" t="n">
-        <v>501</v>
+        <v>1701</v>
       </c>
       <c r="E158" t="n">
-        <v>128.1721108509959</v>
+        <v>477.0787041987936</v>
       </c>
     </row>
     <row r="159">
@@ -3132,13 +3132,13 @@
         <v>101</v>
       </c>
       <c r="C159" t="n">
-        <v>141.2</v>
+        <v>241.1</v>
       </c>
       <c r="D159" t="n">
-        <v>302</v>
+        <v>900</v>
       </c>
       <c r="E159" t="n">
-        <v>80.40000000000001</v>
+        <v>253.6381083354786</v>
       </c>
     </row>
     <row r="160">
@@ -3149,13 +3149,13 @@
         <v>101</v>
       </c>
       <c r="C160" t="n">
-        <v>2561.9</v>
+        <v>161.1</v>
       </c>
       <c r="D160" t="n">
-        <v>23510</v>
+        <v>501</v>
       </c>
       <c r="E160" t="n">
-        <v>6987.275541296478</v>
+        <v>128.172110850996</v>
       </c>
     </row>
     <row r="161">
@@ -3166,13 +3166,13 @@
         <v>101</v>
       </c>
       <c r="C161" t="n">
-        <v>55045737.8</v>
+        <v>84944614.8</v>
       </c>
       <c r="D161" t="n">
-        <v>161970411</v>
+        <v>163741746</v>
       </c>
       <c r="E161" t="n">
-        <v>49679608.40084531</v>
+        <v>51644024.40253184</v>
       </c>
     </row>
     <row r="162">
@@ -3183,13 +3183,13 @@
         <v>101</v>
       </c>
       <c r="C162" t="n">
-        <v>20112073.7</v>
+        <v>45846474.8</v>
       </c>
       <c r="D162" t="n">
-        <v>90005305</v>
+        <v>147320645</v>
       </c>
       <c r="E162" t="n">
-        <v>25576099.6207162</v>
+        <v>47288451.17654774</v>
       </c>
     </row>
     <row r="163">
@@ -3200,13 +3200,13 @@
         <v>101</v>
       </c>
       <c r="C163" t="n">
-        <v>9579443.5</v>
+        <v>11703009.4</v>
       </c>
       <c r="D163" t="n">
-        <v>27821785</v>
+        <v>73335090</v>
       </c>
       <c r="E163" t="n">
-        <v>8407179.952102419</v>
+        <v>23678003.85967471</v>
       </c>
     </row>
     <row r="164">
@@ -3217,13 +3217,13 @@
         <v>101</v>
       </c>
       <c r="C164" t="n">
-        <v>3925714</v>
+        <v>16296.7</v>
       </c>
       <c r="D164" t="n">
-        <v>10306148</v>
+        <v>103729</v>
       </c>
       <c r="E164" t="n">
-        <v>3640782.156282658</v>
+        <v>31609.82359979252</v>
       </c>
     </row>
     <row r="165">
@@ -3234,13 +3234,13 @@
         <v>101</v>
       </c>
       <c r="C165" t="n">
-        <v>1691893.5</v>
+        <v>281</v>
       </c>
       <c r="D165" t="n">
-        <v>6367042</v>
+        <v>1001</v>
       </c>
       <c r="E165" t="n">
-        <v>2471253.909178223</v>
+        <v>336.838536987679</v>
       </c>
     </row>
     <row r="166">
@@ -3251,13 +3251,13 @@
         <v>101</v>
       </c>
       <c r="C166" t="n">
-        <v>206253.2</v>
+        <v>331.1</v>
       </c>
       <c r="D166" t="n">
-        <v>2059523</v>
+        <v>1002</v>
       </c>
       <c r="E166" t="n">
-        <v>617756.6517357462</v>
+        <v>331.8949984558369</v>
       </c>
     </row>
     <row r="167">
@@ -3268,13 +3268,13 @@
         <v>101</v>
       </c>
       <c r="C167" t="n">
-        <v>131.1</v>
+        <v>231.4</v>
       </c>
       <c r="D167" t="n">
-        <v>302</v>
+        <v>502</v>
       </c>
       <c r="E167" t="n">
-        <v>64.29688950485863</v>
+        <v>179.4336646228907</v>
       </c>
     </row>
     <row r="168">
@@ -3285,13 +3285,13 @@
         <v>101</v>
       </c>
       <c r="C168" t="n">
-        <v>211.1</v>
+        <v>551.4</v>
       </c>
       <c r="D168" t="n">
-        <v>900</v>
+        <v>2904</v>
       </c>
       <c r="E168" t="n">
-        <v>238.2819548350231</v>
+        <v>824.4762216098169</v>
       </c>
     </row>
     <row r="169">
@@ -3302,13 +3302,13 @@
         <v>101</v>
       </c>
       <c r="C169" t="n">
-        <v>181.4</v>
+        <v>731.6</v>
       </c>
       <c r="D169" t="n">
-        <v>502</v>
+        <v>5106</v>
       </c>
       <c r="E169" t="n">
-        <v>125.2846359295504</v>
+        <v>1479.28578712837</v>
       </c>
     </row>
     <row r="170">
@@ -3319,13 +3319,13 @@
         <v>101</v>
       </c>
       <c r="C170" t="n">
-        <v>121.2</v>
+        <v>111.2</v>
       </c>
       <c r="D170" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E170" t="n">
-        <v>40.4</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="171">
@@ -3336,13 +3336,13 @@
         <v>101</v>
       </c>
       <c r="C171" t="n">
-        <v>211.1</v>
+        <v>241.1</v>
       </c>
       <c r="D171" t="n">
         <v>900</v>
       </c>
       <c r="E171" t="n">
-        <v>238.2819548350231</v>
+        <v>249.6242976955569</v>
       </c>
     </row>
     <row r="172">
@@ -3353,13 +3353,13 @@
         <v>101</v>
       </c>
       <c r="C172" t="n">
-        <v>211.1</v>
+        <v>221.1</v>
       </c>
       <c r="D172" t="n">
-        <v>900</v>
+        <v>1101</v>
       </c>
       <c r="E172" t="n">
-        <v>238.2819548350231</v>
+        <v>299.3594661940725</v>
       </c>
     </row>
     <row r="173">
@@ -3370,13 +3370,13 @@
         <v>101</v>
       </c>
       <c r="C173" t="n">
-        <v>361.1</v>
+        <v>221.2</v>
       </c>
       <c r="D173" t="n">
-        <v>1701</v>
+        <v>1102</v>
       </c>
       <c r="E173" t="n">
-        <v>520.123148879186</v>
+        <v>296.2636663514444</v>
       </c>
     </row>
     <row r="174">
@@ -3387,13 +3387,13 @@
         <v>101</v>
       </c>
       <c r="C174" t="n">
-        <v>211.2</v>
+        <v>121.1</v>
       </c>
       <c r="D174" t="n">
-        <v>1002</v>
+        <v>302</v>
       </c>
       <c r="E174" t="n">
-        <v>270.3260253841646</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="175">
@@ -3404,13 +3404,13 @@
         <v>101</v>
       </c>
       <c r="C175" t="n">
-        <v>201.3</v>
+        <v>101</v>
       </c>
       <c r="D175" t="n">
-        <v>502</v>
+        <v>101</v>
       </c>
       <c r="E175" t="n">
-        <v>155.306825349049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3421,13 +3421,13 @@
         <v>101</v>
       </c>
       <c r="C176" t="n">
-        <v>301.4</v>
+        <v>191</v>
       </c>
       <c r="D176" t="n">
-        <v>1102</v>
+        <v>1001</v>
       </c>
       <c r="E176" t="n">
-        <v>319.781863150492</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177">
@@ -3438,13 +3438,13 @@
         <v>101</v>
       </c>
       <c r="C177" t="n">
-        <v>280.9</v>
+        <v>191</v>
       </c>
       <c r="D177" t="n">
-        <v>1101</v>
+        <v>501</v>
       </c>
       <c r="E177" t="n">
-        <v>362.5963182383407</v>
+        <v>157.797338380595</v>
       </c>
     </row>
     <row r="178">
@@ -3455,13 +3455,13 @@
         <v>101</v>
       </c>
       <c r="C178" t="n">
-        <v>201.1</v>
+        <v>211</v>
       </c>
       <c r="D178" t="n">
-        <v>1102</v>
+        <v>1001</v>
       </c>
       <c r="E178" t="n">
-        <v>300.3</v>
+        <v>266.270539113887</v>
       </c>
     </row>
     <row r="179">
@@ -3472,13 +3472,13 @@
         <v>101</v>
       </c>
       <c r="C179" t="n">
-        <v>271.1</v>
+        <v>161.2</v>
       </c>
       <c r="D179" t="n">
-        <v>1701</v>
+        <v>501</v>
       </c>
       <c r="E179" t="n">
-        <v>477.5835947768726</v>
+        <v>120.067314453185</v>
       </c>
     </row>
     <row r="180">
@@ -3489,13 +3489,13 @@
         <v>101</v>
       </c>
       <c r="C180" t="n">
-        <v>221</v>
+        <v>471.8</v>
       </c>
       <c r="D180" t="n">
-        <v>900</v>
+        <v>3005</v>
       </c>
       <c r="E180" t="n">
-        <v>255.9691387648128</v>
+        <v>853.2229251491077</v>
       </c>
     </row>
     <row r="181">
@@ -3506,13 +3506,13 @@
         <v>101</v>
       </c>
       <c r="C181" t="n">
-        <v>75494306.2</v>
+        <v>44921636.1</v>
       </c>
       <c r="D181" t="n">
-        <v>161490495</v>
+        <v>105279341</v>
       </c>
       <c r="E181" t="n">
-        <v>52533681.30303305</v>
+        <v>36287083.34939189</v>
       </c>
     </row>
     <row r="182">
@@ -3523,13 +3523,13 @@
         <v>101</v>
       </c>
       <c r="C182" t="n">
-        <v>28696469.5</v>
+        <v>12017386.7</v>
       </c>
       <c r="D182" t="n">
-        <v>112694239</v>
+        <v>42949598</v>
       </c>
       <c r="E182" t="n">
-        <v>33802894.25571122</v>
+        <v>13246749.90785631</v>
       </c>
     </row>
     <row r="183">
@@ -3540,13 +3540,13 @@
         <v>101</v>
       </c>
       <c r="C183" t="n">
-        <v>5347777.7</v>
+        <v>1877779.6</v>
       </c>
       <c r="D183" t="n">
-        <v>27775986</v>
+        <v>8510245</v>
       </c>
       <c r="E183" t="n">
-        <v>10609950.41665939</v>
+        <v>2566924.468535808</v>
       </c>
     </row>
     <row r="184">
@@ -3557,13 +3557,13 @@
         <v>101</v>
       </c>
       <c r="C184" t="n">
-        <v>5953.6</v>
+        <v>415142.7</v>
       </c>
       <c r="D184" t="n">
-        <v>53425</v>
+        <v>3103721</v>
       </c>
       <c r="E184" t="n">
-        <v>15849.2110794197</v>
+        <v>942867.1398573661</v>
       </c>
     </row>
     <row r="185">
@@ -3574,13 +3574,13 @@
         <v>101</v>
       </c>
       <c r="C185" t="n">
-        <v>340.9</v>
+        <v>181.1</v>
       </c>
       <c r="D185" t="n">
-        <v>1701</v>
+        <v>902</v>
       </c>
       <c r="E185" t="n">
-        <v>512.1406935598849</v>
+        <v>240.3</v>
       </c>
     </row>
     <row r="186">
@@ -3591,13 +3591,13 @@
         <v>101</v>
       </c>
       <c r="C186" t="n">
-        <v>171.2</v>
+        <v>141.2</v>
       </c>
       <c r="D186" t="n">
-        <v>501</v>
+        <v>302</v>
       </c>
       <c r="E186" t="n">
-        <v>127.0124403355829</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="187">
@@ -3608,13 +3608,13 @@
         <v>101</v>
       </c>
       <c r="C187" t="n">
-        <v>180.9</v>
+        <v>571.4</v>
       </c>
       <c r="D187" t="n">
-        <v>900</v>
+        <v>2904</v>
       </c>
       <c r="E187" t="n">
-        <v>239.7</v>
+        <v>863.4725473343087</v>
       </c>
     </row>
     <row r="188">
@@ -3625,13 +3625,13 @@
         <v>101</v>
       </c>
       <c r="C188" t="n">
-        <v>141.2</v>
+        <v>811.6</v>
       </c>
       <c r="D188" t="n">
-        <v>402</v>
+        <v>5305</v>
       </c>
       <c r="E188" t="n">
-        <v>92.00086956110795</v>
+        <v>1523.295585236168</v>
       </c>
     </row>
     <row r="189">
@@ -3642,13 +3642,13 @@
         <v>101</v>
       </c>
       <c r="C189" t="n">
-        <v>151.3</v>
+        <v>351.1</v>
       </c>
       <c r="D189" t="n">
-        <v>503</v>
+        <v>1803</v>
       </c>
       <c r="E189" t="n">
-        <v>121.0388780516409</v>
+        <v>539.4168054482545</v>
       </c>
     </row>
     <row r="190">
@@ -3676,13 +3676,13 @@
         <v>101</v>
       </c>
       <c r="C191" t="n">
-        <v>341.3</v>
+        <v>591.4</v>
       </c>
       <c r="D191" t="n">
-        <v>1102</v>
+        <v>2904</v>
       </c>
       <c r="E191" t="n">
-        <v>398.417130655799</v>
+        <v>840.4100427767388</v>
       </c>
     </row>
     <row r="192">
@@ -3693,13 +3693,13 @@
         <v>101</v>
       </c>
       <c r="C192" t="n">
-        <v>581.6</v>
+        <v>151.2</v>
       </c>
       <c r="D192" t="n">
-        <v>3505</v>
+        <v>502</v>
       </c>
       <c r="E192" t="n">
-        <v>1021.775630948399</v>
+        <v>120.748333321831</v>
       </c>
     </row>
     <row r="193">
@@ -3710,13 +3710,13 @@
         <v>101</v>
       </c>
       <c r="C193" t="n">
-        <v>261.4</v>
+        <v>601.2</v>
       </c>
       <c r="D193" t="n">
-        <v>502</v>
+        <v>1701</v>
       </c>
       <c r="E193" t="n">
-        <v>196.4490773712109</v>
+        <v>720.9994174754928</v>
       </c>
     </row>
     <row r="194">
@@ -3727,13 +3727,13 @@
         <v>101</v>
       </c>
       <c r="C194" t="n">
-        <v>851.6</v>
+        <v>281.1</v>
       </c>
       <c r="D194" t="n">
-        <v>6905</v>
+        <v>1701</v>
       </c>
       <c r="E194" t="n">
-        <v>2021.672931015301</v>
+        <v>477.0787041987936</v>
       </c>
     </row>
     <row r="195">
@@ -3744,13 +3744,13 @@
         <v>101</v>
       </c>
       <c r="C195" t="n">
-        <v>471.6</v>
+        <v>101</v>
       </c>
       <c r="D195" t="n">
-        <v>2702</v>
+        <v>101</v>
       </c>
       <c r="E195" t="n">
-        <v>763.1621321842431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -3761,13 +3761,13 @@
         <v>101</v>
       </c>
       <c r="C196" t="n">
-        <v>121.1</v>
+        <v>101</v>
       </c>
       <c r="D196" t="n">
-        <v>302</v>
+        <v>101</v>
       </c>
       <c r="E196" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -3778,13 +3778,13 @@
         <v>101</v>
       </c>
       <c r="C197" t="n">
-        <v>101</v>
+        <v>301.1</v>
       </c>
       <c r="D197" t="n">
-        <v>101</v>
+        <v>1102</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>357.827178956546</v>
       </c>
     </row>
     <row r="198">
@@ -3795,13 +3795,13 @@
         <v>101</v>
       </c>
       <c r="C198" t="n">
-        <v>151.2</v>
+        <v>161.2</v>
       </c>
       <c r="D198" t="n">
         <v>502</v>
       </c>
       <c r="E198" t="n">
-        <v>120.748333321831</v>
+        <v>128.4373777371681</v>
       </c>
     </row>
     <row r="199">
@@ -3812,13 +3812,13 @@
         <v>101</v>
       </c>
       <c r="C199" t="n">
-        <v>121.1</v>
+        <v>101</v>
       </c>
       <c r="D199" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="E199" t="n">
-        <v>40.20062188573704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -3829,13 +3829,13 @@
         <v>101</v>
       </c>
       <c r="C200" t="n">
-        <v>201.3</v>
+        <v>111.1</v>
       </c>
       <c r="D200" t="n">
-        <v>502</v>
+        <v>202</v>
       </c>
       <c r="E200" t="n">
-        <v>155.306825349049</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="201">
@@ -3846,13 +3846,13 @@
         <v>101</v>
       </c>
       <c r="C201" t="n">
-        <v>59030877.2</v>
+        <v>55657022.4</v>
       </c>
       <c r="D201" t="n">
-        <v>208763430</v>
+        <v>132914471</v>
       </c>
       <c r="E201" t="n">
-        <v>72182499.85356122</v>
+        <v>37912383.09175506</v>
       </c>
     </row>
     <row r="202">
@@ -3863,13 +3863,13 @@
         <v>101</v>
       </c>
       <c r="C202" t="n">
-        <v>6670280.5</v>
+        <v>23561112.4</v>
       </c>
       <c r="D202" t="n">
-        <v>30148032</v>
+        <v>83898695</v>
       </c>
       <c r="E202" t="n">
-        <v>7998886.785616075</v>
+        <v>23591827.48414678</v>
       </c>
     </row>
     <row r="203">
@@ -3877,16 +3877,16 @@
         <v>1</v>
       </c>
       <c r="B203" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C203" t="n">
-        <v>1855763.6</v>
+        <v>4628423.1</v>
       </c>
       <c r="D203" t="n">
-        <v>5280591</v>
+        <v>31841664</v>
       </c>
       <c r="E203" t="n">
-        <v>1765209.506665212</v>
+        <v>9352154.218083151</v>
       </c>
     </row>
     <row r="204">
@@ -3894,16 +3894,16 @@
         <v>2</v>
       </c>
       <c r="B204" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C204" t="n">
-        <v>6080.6</v>
+        <v>5921.2</v>
       </c>
       <c r="D204" t="n">
-        <v>25600</v>
+        <v>57701</v>
       </c>
       <c r="E204" t="n">
-        <v>9295.336693202673</v>
+        <v>17260.34102096479</v>
       </c>
     </row>
     <row r="205">
@@ -3911,16 +3911,16 @@
         <v>3</v>
       </c>
       <c r="B205" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C205" t="n">
-        <v>110.3</v>
+        <v>921.6</v>
       </c>
       <c r="D205" t="n">
-        <v>201</v>
+        <v>5305</v>
       </c>
       <c r="E205" t="n">
-        <v>30.2359058074998</v>
+        <v>1532.748459467502</v>
       </c>
     </row>
     <row r="206">
@@ -3928,16 +3928,16 @@
         <v>4</v>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C206" t="n">
-        <v>230.3</v>
+        <v>111</v>
       </c>
       <c r="D206" t="n">
-        <v>900</v>
+        <v>201</v>
       </c>
       <c r="E206" t="n">
-        <v>279.7541956789925</v>
+        <v>30</v>
       </c>
     </row>
     <row r="207">
@@ -3945,16 +3945,16 @@
         <v>5</v>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C207" t="n">
-        <v>70.09999999999999</v>
+        <v>291.3</v>
       </c>
       <c r="D207" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E207" t="n">
-        <v>64.23464797132463</v>
+        <v>311.6828676716127</v>
       </c>
     </row>
     <row r="208">
@@ -3962,16 +3962,16 @@
         <v>6</v>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C208" t="n">
-        <v>160.2</v>
+        <v>181.2</v>
       </c>
       <c r="D208" t="n">
-        <v>1001</v>
+        <v>602</v>
       </c>
       <c r="E208" t="n">
-        <v>287.3606792865023</v>
+        <v>153.9745433505162</v>
       </c>
     </row>
     <row r="209">
@@ -3979,16 +3979,16 @@
         <v>7</v>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C209" t="n">
-        <v>170.3</v>
+        <v>180.9</v>
       </c>
       <c r="D209" t="n">
-        <v>1102</v>
+        <v>900</v>
       </c>
       <c r="E209" t="n">
-        <v>323.2621382098436</v>
+        <v>239.7</v>
       </c>
     </row>
     <row r="210">
@@ -3996,16 +3996,16 @@
         <v>8</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C210" t="n">
-        <v>130.2</v>
+        <v>1881.9</v>
       </c>
       <c r="D210" t="n">
-        <v>1001</v>
+        <v>15309</v>
       </c>
       <c r="E210" t="n">
-        <v>297.133236107979</v>
+        <v>4503.199050674975</v>
       </c>
     </row>
     <row r="211">
@@ -4013,16 +4013,16 @@
         <v>9</v>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C211" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>236.3476253318404</v>
       </c>
     </row>
     <row r="212">
@@ -4030,16 +4030,16 @@
         <v>10</v>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C212" t="n">
-        <v>120.2</v>
+        <v>201.3</v>
       </c>
       <c r="D212" t="n">
-        <v>1001</v>
+        <v>502</v>
       </c>
       <c r="E212" t="n">
-        <v>299.6533997804797</v>
+        <v>141.8457260547529</v>
       </c>
     </row>
     <row r="213">
@@ -4047,16 +4047,16 @@
         <v>11</v>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C213" t="n">
-        <v>20.1</v>
+        <v>191.2</v>
       </c>
       <c r="D213" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E213" t="n">
-        <v>60.3</v>
+        <v>158.1902651872106</v>
       </c>
     </row>
     <row r="214">
@@ -4064,16 +4064,16 @@
         <v>12</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C214" t="n">
-        <v>240.4</v>
+        <v>451.6</v>
       </c>
       <c r="D214" t="n">
-        <v>1001</v>
+        <v>2904</v>
       </c>
       <c r="E214" t="n">
-        <v>388.1858317867874</v>
+        <v>826.9829744317595</v>
       </c>
     </row>
     <row r="215">
@@ -4081,16 +4081,16 @@
         <v>13</v>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C215" t="n">
-        <v>80.5</v>
+        <v>131.3</v>
       </c>
       <c r="D215" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E215" t="n">
-        <v>87.63703555004585</v>
+        <v>46.28401451905398</v>
       </c>
     </row>
     <row r="216">
@@ -4098,16 +4098,16 @@
         <v>14</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C216" t="n">
-        <v>30.3</v>
+        <v>121.2</v>
       </c>
       <c r="D216" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="E216" t="n">
-        <v>46.28401451905398</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="217">
@@ -4115,16 +4115,16 @@
         <v>15</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C217" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="D217" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E217" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -4132,16 +4132,16 @@
         <v>16</v>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>131.2</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="219">
@@ -4149,16 +4149,16 @@
         <v>17</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C219" t="n">
-        <v>740.7</v>
+        <v>561.6</v>
       </c>
       <c r="D219" t="n">
-        <v>6804</v>
+        <v>2904</v>
       </c>
       <c r="E219" t="n">
-        <v>2025.093975597182</v>
+        <v>829.3785866538875</v>
       </c>
     </row>
     <row r="220">
@@ -4166,16 +4166,16 @@
         <v>18</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C220" t="n">
-        <v>30.2</v>
+        <v>101</v>
       </c>
       <c r="D220" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E220" t="n">
-        <v>64.40621088062859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -4183,16 +4183,16 @@
         <v>19</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C221" t="n">
-        <v>76154002.90000001</v>
+        <v>65886488.4</v>
       </c>
       <c r="D221" t="n">
-        <v>170740945</v>
+        <v>193153894</v>
       </c>
       <c r="E221" t="n">
-        <v>56791707.24665677</v>
+        <v>63864139.99791557</v>
       </c>
     </row>
     <row r="222">
@@ -4200,16 +4200,16 @@
         <v>20</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C222" t="n">
-        <v>24188660.3</v>
+        <v>9147042</v>
       </c>
       <c r="D222" t="n">
-        <v>90858655</v>
+        <v>35726245</v>
       </c>
       <c r="E222" t="n">
-        <v>34271324.65495689</v>
+        <v>14368968.53055332</v>
       </c>
     </row>
     <row r="223">
@@ -4217,16 +4217,16 @@
         <v>21</v>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C223" t="n">
-        <v>1758154.6</v>
+        <v>81052.10000000001</v>
       </c>
       <c r="D223" t="n">
-        <v>4466684</v>
+        <v>410155</v>
       </c>
       <c r="E223" t="n">
-        <v>2083976.863400033</v>
+        <v>161327.8114953835</v>
       </c>
     </row>
     <row r="224">
@@ -4234,16 +4234,16 @@
         <v>22</v>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C224" t="n">
-        <v>45865.2</v>
+        <v>321.1</v>
       </c>
       <c r="D224" t="n">
-        <v>188726</v>
+        <v>1102</v>
       </c>
       <c r="E224" t="n">
-        <v>56686.58205219291</v>
+        <v>362.8722778058417</v>
       </c>
     </row>
     <row r="225">
@@ -4251,16 +4251,16 @@
         <v>23</v>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C225" t="n">
-        <v>11902</v>
+        <v>141.1</v>
       </c>
       <c r="D225" t="n">
-        <v>59216</v>
+        <v>502</v>
       </c>
       <c r="E225" t="n">
-        <v>23308.86917462965</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="226">
@@ -4268,16 +4268,16 @@
         <v>24</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C226" t="n">
-        <v>130.3</v>
+        <v>231.1</v>
       </c>
       <c r="D226" t="n">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="E226" t="n">
-        <v>297.1232235958677</v>
+        <v>236.6311264394437</v>
       </c>
     </row>
     <row r="227">
@@ -4285,16 +4285,16 @@
         <v>25</v>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C227" t="n">
-        <v>60.3</v>
+        <v>131.2</v>
       </c>
       <c r="D227" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E227" t="n">
-        <v>92.10977146861238</v>
+        <v>64.40621088062858</v>
       </c>
     </row>
     <row r="228">
@@ -4302,16 +4302,16 @@
         <v>26</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C228" t="n">
-        <v>190.3</v>
+        <v>111.1</v>
       </c>
       <c r="D228" t="n">
-        <v>901</v>
+        <v>202</v>
       </c>
       <c r="E228" t="n">
-        <v>356.603715628427</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="229">
@@ -4319,16 +4319,16 @@
         <v>27</v>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C229" t="n">
-        <v>250.5</v>
+        <v>421.4</v>
       </c>
       <c r="D229" t="n">
-        <v>901</v>
+        <v>2904</v>
       </c>
       <c r="E229" t="n">
-        <v>335.7532576163633</v>
+        <v>836.124894976821</v>
       </c>
     </row>
     <row r="230">
@@ -4336,16 +4336,16 @@
         <v>28</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C230" t="n">
-        <v>50.1</v>
+        <v>301.1</v>
       </c>
       <c r="D230" t="n">
-        <v>201</v>
+        <v>1701</v>
       </c>
       <c r="E230" t="n">
-        <v>67.30594327397841</v>
+        <v>481.7053975201026</v>
       </c>
     </row>
     <row r="231">
@@ -4353,16 +4353,16 @@
         <v>29</v>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C231" t="n">
-        <v>50.2</v>
+        <v>111</v>
       </c>
       <c r="D231" t="n">
         <v>201</v>
       </c>
       <c r="E231" t="n">
-        <v>80.99481464884033</v>
+        <v>30</v>
       </c>
     </row>
     <row r="232">
@@ -4370,16 +4370,16 @@
         <v>30</v>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C232" t="n">
-        <v>100.1</v>
+        <v>161.2</v>
       </c>
       <c r="D232" t="n">
-        <v>1001</v>
+        <v>502</v>
       </c>
       <c r="E232" t="n">
-        <v>300.3</v>
+        <v>128.4373777371681</v>
       </c>
     </row>
     <row r="233">
@@ -4387,16 +4387,16 @@
         <v>31</v>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C233" t="n">
-        <v>680.4</v>
+        <v>221.2</v>
       </c>
       <c r="D233" t="n">
-        <v>6804</v>
+        <v>900</v>
       </c>
       <c r="E233" t="n">
-        <v>2041.2</v>
+        <v>243.9109673630934</v>
       </c>
     </row>
     <row r="234">
@@ -4404,16 +4404,16 @@
         <v>32</v>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C234" t="n">
-        <v>840.8</v>
+        <v>261</v>
       </c>
       <c r="D234" t="n">
-        <v>6804</v>
+        <v>1701</v>
       </c>
       <c r="E234" t="n">
-        <v>2008.685480606658</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235">
@@ -4421,16 +4421,16 @@
         <v>33</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C235" t="n">
-        <v>40.2</v>
+        <v>821.6</v>
       </c>
       <c r="D235" t="n">
-        <v>201</v>
+        <v>6505</v>
       </c>
       <c r="E235" t="n">
-        <v>80.40000000000001</v>
+        <v>1901.056927080302</v>
       </c>
     </row>
     <row r="236">
@@ -4438,16 +4438,16 @@
         <v>34</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C236" t="n">
-        <v>140.4</v>
+        <v>601.5</v>
       </c>
       <c r="D236" t="n">
-        <v>1001</v>
+        <v>2904</v>
       </c>
       <c r="E236" t="n">
-        <v>294.2248120060577</v>
+        <v>900.7224045176183</v>
       </c>
     </row>
     <row r="237">
@@ -4455,16 +4455,16 @@
         <v>35</v>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C237" t="n">
-        <v>10</v>
+        <v>190.9</v>
       </c>
       <c r="D237" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="E237" t="n">
-        <v>30</v>
+        <v>238.2395643045042</v>
       </c>
     </row>
     <row r="238">
@@ -4472,16 +4472,16 @@
         <v>36</v>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C238" t="n">
-        <v>10</v>
+        <v>461.2</v>
       </c>
       <c r="D238" t="n">
-        <v>100</v>
+        <v>2904</v>
       </c>
       <c r="E238" t="n">
-        <v>30</v>
+        <v>848.3966996635478</v>
       </c>
     </row>
     <row r="239">
@@ -4489,16 +4489,16 @@
         <v>37</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C239" t="n">
-        <v>140.2</v>
+        <v>131.1</v>
       </c>
       <c r="D239" t="n">
-        <v>1001</v>
+        <v>302</v>
       </c>
       <c r="E239" t="n">
-        <v>294.2518649048804</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="240">
@@ -4506,16 +4506,16 @@
         <v>38</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C240" t="n">
-        <v>40.1</v>
+        <v>290.9</v>
       </c>
       <c r="D240" t="n">
-        <v>201</v>
+        <v>900</v>
       </c>
       <c r="E240" t="n">
-        <v>66.57394385193054</v>
+        <v>310.8991637171126</v>
       </c>
     </row>
     <row r="241">
@@ -4523,16 +4523,16 @@
         <v>39</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C241" t="n">
-        <v>69924073.40000001</v>
+        <v>72970110</v>
       </c>
       <c r="D241" t="n">
-        <v>192397501</v>
+        <v>131448918</v>
       </c>
       <c r="E241" t="n">
-        <v>77255229.57477748</v>
+        <v>41952378.03530367</v>
       </c>
     </row>
     <row r="242">
@@ -4540,16 +4540,16 @@
         <v>40</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C242" t="n">
-        <v>922346.2</v>
+        <v>26139876.3</v>
       </c>
       <c r="D242" t="n">
-        <v>5293446</v>
+        <v>113054087</v>
       </c>
       <c r="E242" t="n">
-        <v>1589428.8881663</v>
+        <v>34533098.47569845</v>
       </c>
     </row>
     <row r="243">
@@ -4557,16 +4557,16 @@
         <v>41</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C243" t="n">
-        <v>70381.89999999999</v>
+        <v>1774106.7</v>
       </c>
       <c r="D243" t="n">
-        <v>695013</v>
+        <v>15956662</v>
       </c>
       <c r="E243" t="n">
-        <v>208226.0882115639</v>
+        <v>4747315.923385362</v>
       </c>
     </row>
     <row r="244">
@@ -4574,16 +4574,16 @@
         <v>42</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C244" t="n">
-        <v>110.2</v>
+        <v>165515.2</v>
       </c>
       <c r="D244" t="n">
-        <v>1001</v>
+        <v>1467205</v>
       </c>
       <c r="E244" t="n">
-        <v>298.456294957905</v>
+        <v>435173.4201804609</v>
       </c>
     </row>
     <row r="245">
@@ -4591,16 +4591,16 @@
         <v>43</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C245" t="n">
-        <v>120.2</v>
+        <v>2271.9</v>
       </c>
       <c r="D245" t="n">
-        <v>1001</v>
+        <v>20510</v>
       </c>
       <c r="E245" t="n">
-        <v>299.6533997804797</v>
+        <v>6084.475449042423</v>
       </c>
     </row>
     <row r="246">
@@ -4608,16 +4608,16 @@
         <v>44</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C246" t="n">
-        <v>120.2</v>
+        <v>231.3</v>
       </c>
       <c r="D246" t="n">
-        <v>1001</v>
+        <v>603</v>
       </c>
       <c r="E246" t="n">
-        <v>299.6533997804797</v>
+        <v>200.7546014416606</v>
       </c>
     </row>
     <row r="247">
@@ -4625,16 +4625,16 @@
         <v>45</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C247" t="n">
-        <v>150.3</v>
+        <v>261</v>
       </c>
       <c r="D247" t="n">
-        <v>1001</v>
+        <v>1701</v>
       </c>
       <c r="E247" t="n">
-        <v>301.1813573247853</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248">
@@ -4642,16 +4642,16 @@
         <v>46</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C248" t="n">
-        <v>120.2</v>
+        <v>461.1</v>
       </c>
       <c r="D248" t="n">
-        <v>1202</v>
+        <v>1701</v>
       </c>
       <c r="E248" t="n">
-        <v>360.6</v>
+        <v>631.1957620263305</v>
       </c>
     </row>
     <row r="249">
@@ -4659,13 +4659,13 @@
         <v>47</v>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
@@ -4676,16 +4676,16 @@
         <v>48</v>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C250" t="n">
-        <v>30.1</v>
+        <v>261</v>
       </c>
       <c r="D250" t="n">
-        <v>201</v>
+        <v>1701</v>
       </c>
       <c r="E250" t="n">
-        <v>64.29688950485864</v>
+        <v>480</v>
       </c>
     </row>
     <row r="251">
@@ -4693,16 +4693,16 @@
         <v>49</v>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C251" t="n">
-        <v>110.1</v>
+        <v>301.2</v>
       </c>
       <c r="D251" t="n">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="E251" t="n">
-        <v>298.4595282446181</v>
+        <v>268.3288281195295</v>
       </c>
     </row>
     <row r="252">
@@ -4710,16 +4710,16 @@
         <v>50</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C252" t="n">
-        <v>30.2</v>
+        <v>171.3</v>
       </c>
       <c r="D252" t="n">
-        <v>101</v>
+        <v>402</v>
       </c>
       <c r="E252" t="n">
-        <v>46.13198456602534</v>
+        <v>100.8871151336978</v>
       </c>
     </row>
     <row r="253">
@@ -4727,16 +4727,16 @@
         <v>51</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C253" t="n">
-        <v>120.2</v>
+        <v>221.1</v>
       </c>
       <c r="D253" t="n">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="E253" t="n">
-        <v>299.6533997804797</v>
+        <v>239.7838401560873</v>
       </c>
     </row>
     <row r="254">
@@ -4744,16 +4744,16 @@
         <v>52</v>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C254" t="n">
-        <v>60.3</v>
+        <v>271.4</v>
       </c>
       <c r="D254" t="n">
-        <v>201</v>
+        <v>1002</v>
       </c>
       <c r="E254" t="n">
-        <v>92.10977146861238</v>
+        <v>276.2322211473528</v>
       </c>
     </row>
     <row r="255">
@@ -4761,16 +4761,16 @@
         <v>53</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C255" t="n">
-        <v>30.1</v>
+        <v>291.2</v>
       </c>
       <c r="D255" t="n">
-        <v>101</v>
+        <v>1803</v>
       </c>
       <c r="E255" t="n">
-        <v>45.9792344433876</v>
+        <v>505.4743910427114</v>
       </c>
     </row>
     <row r="256">
@@ -4778,16 +4778,16 @@
         <v>54</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C256" t="n">
-        <v>40.2</v>
+        <v>121.1</v>
       </c>
       <c r="D256" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E256" t="n">
-        <v>66.66453329919891</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="257">
@@ -4795,16 +4795,16 @@
         <v>55</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C257" t="n">
-        <v>300.4</v>
+        <v>211.3</v>
       </c>
       <c r="D257" t="n">
-        <v>1802</v>
+        <v>502</v>
       </c>
       <c r="E257" t="n">
-        <v>581.9969415727199</v>
+        <v>158.2220275435756</v>
       </c>
     </row>
     <row r="258">
@@ -4812,16 +4812,16 @@
         <v>56</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C258" t="n">
-        <v>20.1</v>
+        <v>261.2</v>
       </c>
       <c r="D258" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E258" t="n">
-        <v>60.3</v>
+        <v>332.6502066736168</v>
       </c>
     </row>
     <row r="259">
@@ -4829,16 +4829,16 @@
         <v>57</v>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C259" t="n">
-        <v>40.4</v>
+        <v>220.9</v>
       </c>
       <c r="D259" t="n">
-        <v>201</v>
+        <v>900</v>
       </c>
       <c r="E259" t="n">
-        <v>66.84639107685621</v>
+        <v>255.8595122327876</v>
       </c>
     </row>
     <row r="260">
@@ -4846,16 +4846,16 @@
         <v>58</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C260" t="n">
-        <v>50.3</v>
+        <v>411.7</v>
       </c>
       <c r="D260" t="n">
-        <v>201</v>
+        <v>2904</v>
       </c>
       <c r="E260" t="n">
-        <v>81.05683191440434</v>
+        <v>832.0018088922644</v>
       </c>
     </row>
     <row r="261">
@@ -4863,16 +4863,16 @@
         <v>59</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C261" t="n">
-        <v>41086990.9</v>
+        <v>58126152</v>
       </c>
       <c r="D261" t="n">
-        <v>108177245</v>
+        <v>116370201</v>
       </c>
       <c r="E261" t="n">
-        <v>34887504.8387064</v>
+        <v>32768540.11011717</v>
       </c>
     </row>
     <row r="262">
@@ -4880,16 +4880,16 @@
         <v>60</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C262" t="n">
-        <v>13312905.7</v>
+        <v>31988498.4</v>
       </c>
       <c r="D262" t="n">
-        <v>34734357</v>
+        <v>67958066</v>
       </c>
       <c r="E262" t="n">
-        <v>11718768.72364182</v>
+        <v>28482155.25989002</v>
       </c>
     </row>
     <row r="263">
@@ -4897,16 +4897,16 @@
         <v>61</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C263" t="n">
-        <v>621563.8</v>
+        <v>9357305.800000001</v>
       </c>
       <c r="D263" t="n">
-        <v>3993519</v>
+        <v>60875439</v>
       </c>
       <c r="E263" t="n">
-        <v>1162104.34816679</v>
+        <v>18984403.81471963</v>
       </c>
     </row>
     <row r="264">
@@ -4914,16 +4914,16 @@
         <v>62</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C264" t="n">
-        <v>194929.8</v>
+        <v>84281</v>
       </c>
       <c r="D264" t="n">
-        <v>649766</v>
+        <v>427051</v>
       </c>
       <c r="E264" t="n">
-        <v>297760.1879008676</v>
+        <v>168160.09184762</v>
       </c>
     </row>
     <row r="265">
@@ -4931,16 +4931,16 @@
         <v>63</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C265" t="n">
-        <v>20.1</v>
+        <v>83191.2</v>
       </c>
       <c r="D265" t="n">
-        <v>201</v>
+        <v>414050</v>
       </c>
       <c r="E265" t="n">
-        <v>60.3</v>
+        <v>162841.7857141096</v>
       </c>
     </row>
     <row r="266">
@@ -4948,16 +4948,16 @@
         <v>64</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C266" t="n">
-        <v>120.3</v>
+        <v>201</v>
       </c>
       <c r="D266" t="n">
-        <v>1102</v>
+        <v>900</v>
       </c>
       <c r="E266" t="n">
-        <v>328.6159004065385</v>
+        <v>236.3476253318404</v>
       </c>
     </row>
     <row r="267">
@@ -4965,16 +4965,16 @@
         <v>65</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C267" t="n">
-        <v>30.2</v>
+        <v>111</v>
       </c>
       <c r="D267" t="n">
         <v>201</v>
       </c>
       <c r="E267" t="n">
-        <v>64.40621088062859</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268">
@@ -4982,16 +4982,16 @@
         <v>66</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C268" t="n">
-        <v>40.2</v>
+        <v>141.2</v>
       </c>
       <c r="D268" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E268" t="n">
-        <v>80.40000000000001</v>
+        <v>66.66453329919891</v>
       </c>
     </row>
     <row r="269">
@@ -4999,16 +4999,16 @@
         <v>67</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C269" t="n">
-        <v>10</v>
+        <v>1181.8</v>
       </c>
       <c r="D269" t="n">
-        <v>100</v>
+        <v>6905</v>
       </c>
       <c r="E269" t="n">
-        <v>30</v>
+        <v>2077.713685761346</v>
       </c>
     </row>
     <row r="270">
@@ -5016,16 +5016,16 @@
         <v>68</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C270" t="n">
-        <v>70.3</v>
+        <v>341.3</v>
       </c>
       <c r="D270" t="n">
-        <v>201</v>
+        <v>1403</v>
       </c>
       <c r="E270" t="n">
-        <v>90.43345619846671</v>
+        <v>425.0607133104635</v>
       </c>
     </row>
     <row r="271">
@@ -5033,16 +5033,16 @@
         <v>69</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C271" t="n">
-        <v>40.3</v>
+        <v>181.2</v>
       </c>
       <c r="D271" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E271" t="n">
-        <v>66.75634801275456</v>
+        <v>160.4</v>
       </c>
     </row>
     <row r="272">
@@ -5050,16 +5050,16 @@
         <v>70</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C272" t="n">
-        <v>120.3</v>
+        <v>411.4</v>
       </c>
       <c r="D272" t="n">
-        <v>1001</v>
+        <v>2904</v>
       </c>
       <c r="E272" t="n">
-        <v>299.6805132136556</v>
+        <v>832.0774242821398</v>
       </c>
     </row>
     <row r="273">
@@ -5067,16 +5067,16 @@
         <v>71</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C273" t="n">
-        <v>20.1</v>
+        <v>111</v>
       </c>
       <c r="D273" t="n">
         <v>201</v>
       </c>
       <c r="E273" t="n">
-        <v>60.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274">
@@ -5084,16 +5084,16 @@
         <v>72</v>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C274" t="n">
-        <v>130.3</v>
+        <v>311.1</v>
       </c>
       <c r="D274" t="n">
-        <v>1001</v>
+        <v>1701</v>
       </c>
       <c r="E274" t="n">
-        <v>297.1232235958677</v>
+        <v>486.7834117962526</v>
       </c>
     </row>
     <row r="275">
@@ -5101,16 +5101,16 @@
         <v>73</v>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C275" t="n">
-        <v>40.2</v>
+        <v>291.2</v>
       </c>
       <c r="D275" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E275" t="n">
-        <v>80.40000000000001</v>
+        <v>381.0566362104195</v>
       </c>
     </row>
     <row r="276">
@@ -5118,16 +5118,16 @@
         <v>74</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C276" t="n">
-        <v>40.2</v>
+        <v>101</v>
       </c>
       <c r="D276" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E276" t="n">
-        <v>66.66453329919891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -5135,16 +5135,16 @@
         <v>75</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C277" t="n">
-        <v>680.4</v>
+        <v>731.8</v>
       </c>
       <c r="D277" t="n">
-        <v>6804</v>
+        <v>6309</v>
       </c>
       <c r="E277" t="n">
-        <v>2041.2</v>
+        <v>1859.305719885785</v>
       </c>
     </row>
     <row r="278">
@@ -5152,16 +5152,16 @@
         <v>76</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C278" t="n">
-        <v>110.2</v>
+        <v>511.5</v>
       </c>
       <c r="D278" t="n">
-        <v>1001</v>
+        <v>2904</v>
       </c>
       <c r="E278" t="n">
-        <v>298.456294957905</v>
+        <v>845.2401138138204</v>
       </c>
     </row>
     <row r="279">
@@ -5169,16 +5169,16 @@
         <v>77</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C279" t="n">
-        <v>250.3</v>
+        <v>111</v>
       </c>
       <c r="D279" t="n">
-        <v>1402</v>
+        <v>201</v>
       </c>
       <c r="E279" t="n">
-        <v>484.8818515886113</v>
+        <v>30</v>
       </c>
     </row>
     <row r="280">
@@ -5186,16 +5186,16 @@
         <v>78</v>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C280" t="n">
-        <v>130.2</v>
+        <v>421.4</v>
       </c>
       <c r="D280" t="n">
-        <v>1001</v>
+        <v>3105</v>
       </c>
       <c r="E280" t="n">
-        <v>297.133236107979</v>
+        <v>895.4023899901094</v>
       </c>
     </row>
     <row r="281">
@@ -5203,16 +5203,16 @@
         <v>79</v>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C281" t="n">
-        <v>42038831.7</v>
+        <v>54537300.7</v>
       </c>
       <c r="D281" t="n">
-        <v>142654843</v>
+        <v>128994662</v>
       </c>
       <c r="E281" t="n">
-        <v>41615364.9674199</v>
+        <v>45547515.50048949</v>
       </c>
     </row>
     <row r="282">
@@ -5220,16 +5220,16 @@
         <v>80</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C282" t="n">
-        <v>8505572.6</v>
+        <v>4558116.8</v>
       </c>
       <c r="D282" t="n">
-        <v>25155210</v>
+        <v>11431726</v>
       </c>
       <c r="E282" t="n">
-        <v>9351585.926010339</v>
+        <v>3489755.878994913</v>
       </c>
     </row>
     <row r="283">
@@ -5237,16 +5237,16 @@
         <v>81</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C283" t="n">
-        <v>1758659.1</v>
+        <v>1190090.6</v>
       </c>
       <c r="D283" t="n">
-        <v>8753270</v>
+        <v>3819670</v>
       </c>
       <c r="E283" t="n">
-        <v>3486000.604479077</v>
+        <v>1185209.001662171</v>
       </c>
     </row>
     <row r="284">
@@ -5254,16 +5254,16 @@
         <v>82</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C284" t="n">
-        <v>11182.8</v>
+        <v>1821.9</v>
       </c>
       <c r="D284" t="n">
-        <v>111425</v>
+        <v>15309</v>
       </c>
       <c r="E284" t="n">
-        <v>33414.16117696208</v>
+        <v>4503.430946511782</v>
       </c>
     </row>
     <row r="285">
@@ -5271,16 +5271,16 @@
         <v>83</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C285" t="n">
-        <v>200.2</v>
+        <v>161.3</v>
       </c>
       <c r="D285" t="n">
-        <v>1001</v>
+        <v>603</v>
       </c>
       <c r="E285" t="n">
-        <v>400.4</v>
+        <v>150.281103269839</v>
       </c>
     </row>
     <row r="286">
@@ -5288,16 +5288,16 @@
         <v>84</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C286" t="n">
-        <v>120.2</v>
+        <v>881.6</v>
       </c>
       <c r="D286" t="n">
-        <v>1001</v>
+        <v>6505</v>
       </c>
       <c r="E286" t="n">
-        <v>299.6533997804797</v>
+        <v>1899.490837040284</v>
       </c>
     </row>
     <row r="287">
@@ -5305,16 +5305,16 @@
         <v>85</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C287" t="n">
-        <v>130.3</v>
+        <v>171.2</v>
       </c>
       <c r="D287" t="n">
-        <v>1001</v>
+        <v>502</v>
       </c>
       <c r="E287" t="n">
-        <v>297.1232235958677</v>
+        <v>127.2484184577553</v>
       </c>
     </row>
     <row r="288">
@@ -5322,13 +5322,13 @@
         <v>86</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C288" t="n">
-        <v>20.1</v>
+        <v>121.1</v>
       </c>
       <c r="D288" t="n">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="E288" t="n">
         <v>40.20062188573704</v>
@@ -5339,16 +5339,16 @@
         <v>87</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1901</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>568.2429058070149</v>
       </c>
     </row>
     <row r="290">
@@ -5356,16 +5356,16 @@
         <v>88</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C290" t="n">
-        <v>20.1</v>
+        <v>531.5</v>
       </c>
       <c r="D290" t="n">
-        <v>201</v>
+        <v>2904</v>
       </c>
       <c r="E290" t="n">
-        <v>60.3</v>
+        <v>847.1309520965457</v>
       </c>
     </row>
     <row r="291">
@@ -5373,16 +5373,16 @@
         <v>89</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C291" t="n">
-        <v>10.1</v>
+        <v>391.2</v>
       </c>
       <c r="D291" t="n">
-        <v>101</v>
+        <v>2601</v>
       </c>
       <c r="E291" t="n">
-        <v>30.3</v>
+        <v>740.8536697621198</v>
       </c>
     </row>
     <row r="292">
@@ -5390,16 +5390,16 @@
         <v>90</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C292" t="n">
-        <v>30.1</v>
+        <v>161.2</v>
       </c>
       <c r="D292" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E292" t="n">
-        <v>64.29688950485863</v>
+        <v>128.4373777371681</v>
       </c>
     </row>
     <row r="293">
@@ -5407,16 +5407,16 @@
         <v>91</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C293" t="n">
-        <v>110.2</v>
+        <v>111.1</v>
       </c>
       <c r="D293" t="n">
-        <v>901</v>
+        <v>202</v>
       </c>
       <c r="E293" t="n">
-        <v>270.3260253841646</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="294">
@@ -5424,16 +5424,16 @@
         <v>92</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C294" t="n">
-        <v>20.1</v>
+        <v>221</v>
       </c>
       <c r="D294" t="n">
-        <v>201</v>
+        <v>900</v>
       </c>
       <c r="E294" t="n">
-        <v>60.3</v>
+        <v>255.9691387648128</v>
       </c>
     </row>
     <row r="295">
@@ -5441,16 +5441,16 @@
         <v>93</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C295" t="n">
-        <v>10</v>
+        <v>351.2</v>
       </c>
       <c r="D295" t="n">
-        <v>100</v>
+        <v>1002</v>
       </c>
       <c r="E295" t="n">
-        <v>30</v>
+        <v>338.497208260275</v>
       </c>
     </row>
     <row r="296">
@@ -5458,16 +5458,16 @@
         <v>94</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C296" t="n">
-        <v>10</v>
+        <v>161.3</v>
       </c>
       <c r="D296" t="n">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="E296" t="n">
-        <v>30</v>
+        <v>128.7027971724003</v>
       </c>
     </row>
     <row r="297">
@@ -5475,16 +5475,16 @@
         <v>95</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C297" t="n">
-        <v>130.2</v>
+        <v>341.3</v>
       </c>
       <c r="D297" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E297" t="n">
-        <v>329.1020510419222</v>
+        <v>398.417130655799</v>
       </c>
     </row>
     <row r="298">
@@ -5492,16 +5492,16 @@
         <v>96</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C298" t="n">
-        <v>110.1</v>
+        <v>111.1</v>
       </c>
       <c r="D298" t="n">
-        <v>1001</v>
+        <v>202</v>
       </c>
       <c r="E298" t="n">
-        <v>298.4595282446181</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="299">
@@ -5509,16 +5509,16 @@
         <v>97</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C299" t="n">
-        <v>30.1</v>
+        <v>251.5</v>
       </c>
       <c r="D299" t="n">
-        <v>201</v>
+        <v>503</v>
       </c>
       <c r="E299" t="n">
-        <v>64.29688950485863</v>
+        <v>175.0726991852242</v>
       </c>
     </row>
     <row r="300">
@@ -5526,16 +5526,16 @@
         <v>98</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C300" t="n">
-        <v>40.2</v>
+        <v>331.2</v>
       </c>
       <c r="D300" t="n">
-        <v>202</v>
+        <v>1802</v>
       </c>
       <c r="E300" t="n">
-        <v>66.81586637917674</v>
+        <v>506.3478646148318</v>
       </c>
     </row>
     <row r="301">
@@ -5543,16 +5543,16 @@
         <v>99</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C301" t="n">
-        <v>40054215.2</v>
+        <v>40206558.3</v>
       </c>
       <c r="D301" t="n">
-        <v>77642899</v>
+        <v>81236280</v>
       </c>
       <c r="E301" t="n">
-        <v>26333059.55835452</v>
+        <v>31025949.27990711</v>
       </c>
     </row>
     <row r="302">
@@ -5560,16 +5560,16 @@
         <v>0</v>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C302" t="n">
-        <v>8260799.8</v>
+        <v>8370845.2</v>
       </c>
       <c r="D302" t="n">
-        <v>48609227</v>
+        <v>32160326</v>
       </c>
       <c r="E302" t="n">
-        <v>14816124.52236307</v>
+        <v>10127712.56029467</v>
       </c>
     </row>
     <row r="303">
@@ -5577,16 +5577,16 @@
         <v>1</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C303" t="n">
-        <v>750.7</v>
+        <v>1863733.6</v>
       </c>
       <c r="D303" t="n">
-        <v>6804</v>
+        <v>18608809</v>
       </c>
       <c r="E303" t="n">
-        <v>2019.656260357193</v>
+        <v>5581692.528259708</v>
       </c>
     </row>
     <row r="304">
@@ -5594,16 +5594,16 @@
         <v>2</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C304" t="n">
-        <v>0</v>
+        <v>2582.6</v>
       </c>
       <c r="D304" t="n">
-        <v>0</v>
+        <v>6505</v>
       </c>
       <c r="E304" t="n">
-        <v>0</v>
+        <v>2608.031180795199</v>
       </c>
     </row>
     <row r="305">
@@ -5611,16 +5611,16 @@
         <v>3</v>
       </c>
       <c r="B305" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C305" t="n">
-        <v>0</v>
+        <v>501.4</v>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="E305" t="n">
-        <v>0</v>
+        <v>490.3878465051923</v>
       </c>
     </row>
     <row r="306">
@@ -5628,16 +5628,16 @@
         <v>4</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C306" t="n">
-        <v>10.2</v>
+        <v>121</v>
       </c>
       <c r="D306" t="n">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="E306" t="n">
-        <v>30.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="307">
@@ -5645,16 +5645,16 @@
         <v>5</v>
       </c>
       <c r="B307" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C307" t="n">
-        <v>30.1</v>
+        <v>141.1</v>
       </c>
       <c r="D307" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E307" t="n">
-        <v>64.29688950485863</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="308">
@@ -5662,16 +5662,16 @@
         <v>6</v>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C308" t="n">
-        <v>60.2</v>
+        <v>221.1</v>
       </c>
       <c r="D308" t="n">
-        <v>501</v>
+        <v>900</v>
       </c>
       <c r="E308" t="n">
-        <v>149.9871994538201</v>
+        <v>239.7838401560873</v>
       </c>
     </row>
     <row r="309">
@@ -5679,16 +5679,16 @@
         <v>7</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C309" t="n">
-        <v>150.3</v>
+        <v>141.1</v>
       </c>
       <c r="D309" t="n">
-        <v>1001</v>
+        <v>302</v>
       </c>
       <c r="E309" t="n">
-        <v>294.4320125258122</v>
+        <v>66.57394385193054</v>
       </c>
     </row>
     <row r="310">
@@ -5696,16 +5696,16 @@
         <v>8</v>
       </c>
       <c r="B310" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C310" t="n">
-        <v>50.2</v>
+        <v>131.1</v>
       </c>
       <c r="D310" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="E310" t="n">
-        <v>67.38070940558582</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="311">
@@ -5713,16 +5713,16 @@
         <v>9</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C311" t="n">
-        <v>880.6</v>
+        <v>191.1</v>
       </c>
       <c r="D311" t="n">
-        <v>8605</v>
+        <v>1002</v>
       </c>
       <c r="E311" t="n">
-        <v>2575.497280138342</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="312">
@@ -5730,16 +5730,16 @@
         <v>10</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C312" t="n">
-        <v>10</v>
+        <v>161.1</v>
       </c>
       <c r="D312" t="n">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="E312" t="n">
-        <v>30</v>
+        <v>128.1721108509959</v>
       </c>
     </row>
     <row r="313">
@@ -5747,16 +5747,16 @@
         <v>11</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C313" t="n">
-        <v>130.4</v>
+        <v>121.1</v>
       </c>
       <c r="D313" t="n">
-        <v>901</v>
+        <v>202</v>
       </c>
       <c r="E313" t="n">
-        <v>268.879973222254</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="314">
@@ -5764,16 +5764,16 @@
         <v>12</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C314" t="n">
-        <v>40.2</v>
+        <v>381.2</v>
       </c>
       <c r="D314" t="n">
-        <v>201</v>
+        <v>1701</v>
       </c>
       <c r="E314" t="n">
-        <v>80.40000000000001</v>
+        <v>497.4016083608898</v>
       </c>
     </row>
     <row r="315">
@@ -5781,16 +5781,16 @@
         <v>13</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C315" t="n">
-        <v>40.2</v>
+        <v>491.4</v>
       </c>
       <c r="D315" t="n">
-        <v>201</v>
+        <v>3005</v>
       </c>
       <c r="E315" t="n">
-        <v>66.66453329919891</v>
+        <v>871.0853230309875</v>
       </c>
     </row>
     <row r="316">
@@ -5798,16 +5798,16 @@
         <v>14</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C316" t="n">
-        <v>50.1</v>
+        <v>221.1</v>
       </c>
       <c r="D316" t="n">
-        <v>301</v>
+        <v>900</v>
       </c>
       <c r="E316" t="n">
-        <v>92.46669670751736</v>
+        <v>239.7838401560873</v>
       </c>
     </row>
     <row r="317">
@@ -5815,16 +5815,16 @@
         <v>15</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C317" t="n">
-        <v>20</v>
+        <v>121.1</v>
       </c>
       <c r="D317" t="n">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="E317" t="n">
-        <v>40</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="318">
@@ -5832,16 +5832,16 @@
         <v>16</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C318" t="n">
-        <v>30.2</v>
+        <v>111.1</v>
       </c>
       <c r="D318" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E318" t="n">
-        <v>64.40621088062859</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="319">
@@ -5849,16 +5849,16 @@
         <v>17</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C319" t="n">
-        <v>920.8</v>
+        <v>101</v>
       </c>
       <c r="D319" t="n">
-        <v>6804</v>
+        <v>101</v>
       </c>
       <c r="E319" t="n">
-        <v>2009.0568832166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -5866,16 +5866,16 @@
         <v>18</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C320" t="n">
-        <v>20.1</v>
+        <v>141.1</v>
       </c>
       <c r="D320" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E320" t="n">
-        <v>60.3</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="321">
@@ -5883,16 +5883,16 @@
         <v>19</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C321" t="n">
-        <v>77628996.2</v>
+        <v>32465866.3</v>
       </c>
       <c r="D321" t="n">
-        <v>175921529</v>
+        <v>80799275</v>
       </c>
       <c r="E321" t="n">
-        <v>65160895.5092297</v>
+        <v>22422982.52362597</v>
       </c>
     </row>
     <row r="322">
@@ -5900,16 +5900,16 @@
         <v>20</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C322" t="n">
-        <v>34500984.4</v>
+        <v>11564811.7</v>
       </c>
       <c r="D322" t="n">
-        <v>93693222</v>
+        <v>22983978</v>
       </c>
       <c r="E322" t="n">
-        <v>33447914.78341093</v>
+        <v>8205382.39960809</v>
       </c>
     </row>
     <row r="323">
@@ -5917,16 +5917,16 @@
         <v>21</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C323" t="n">
-        <v>15392050.9</v>
+        <v>3531721.5</v>
       </c>
       <c r="D323" t="n">
-        <v>46130984</v>
+        <v>13349674</v>
       </c>
       <c r="E323" t="n">
-        <v>17628549.32926108</v>
+        <v>4253729.851686641</v>
       </c>
     </row>
     <row r="324">
@@ -5934,16 +5934,16 @@
         <v>22</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C324" t="n">
-        <v>4286393.5</v>
+        <v>500683.8</v>
       </c>
       <c r="D324" t="n">
-        <v>24429959</v>
+        <v>4989122</v>
       </c>
       <c r="E324" t="n">
-        <v>7059288.892449837</v>
+        <v>1496152.376715072</v>
       </c>
     </row>
     <row r="325">
@@ -5951,16 +5951,16 @@
         <v>23</v>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C325" t="n">
-        <v>1438878.2</v>
+        <v>571.6</v>
       </c>
       <c r="D325" t="n">
-        <v>8005580</v>
+        <v>3505</v>
       </c>
       <c r="E325" t="n">
-        <v>2369197.692184247</v>
+        <v>993.1552950067779</v>
       </c>
     </row>
     <row r="326">
@@ -5968,16 +5968,16 @@
         <v>24</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C326" t="n">
-        <v>20573</v>
+        <v>321.3</v>
       </c>
       <c r="D326" t="n">
-        <v>132226</v>
+        <v>1402</v>
       </c>
       <c r="E326" t="n">
-        <v>43121.97675199967</v>
+        <v>392.2093956039299</v>
       </c>
     </row>
     <row r="327">
@@ -5985,16 +5985,16 @@
         <v>25</v>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C327" t="n">
-        <v>50.2</v>
+        <v>621.3</v>
       </c>
       <c r="D327" t="n">
-        <v>201</v>
+        <v>1901</v>
       </c>
       <c r="E327" t="n">
-        <v>80.99481464884033</v>
+        <v>709.7523582208094</v>
       </c>
     </row>
     <row r="328">
@@ -6002,16 +6002,16 @@
         <v>26</v>
       </c>
       <c r="B328" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C328" t="n">
-        <v>40.3</v>
+        <v>481.4</v>
       </c>
       <c r="D328" t="n">
-        <v>202</v>
+        <v>2705</v>
       </c>
       <c r="E328" t="n">
-        <v>80.60031017310044</v>
+        <v>783.1332198291681</v>
       </c>
     </row>
     <row r="329">
@@ -6019,16 +6019,16 @@
         <v>27</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C329" t="n">
-        <v>20</v>
+        <v>131.1</v>
       </c>
       <c r="D329" t="n">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="E329" t="n">
-        <v>40</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="330">
@@ -6036,16 +6036,16 @@
         <v>28</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C330" t="n">
-        <v>40.2</v>
+        <v>201.3</v>
       </c>
       <c r="D330" t="n">
-        <v>201</v>
+        <v>603</v>
       </c>
       <c r="E330" t="n">
-        <v>80.40000000000001</v>
+        <v>179.500445681898</v>
       </c>
     </row>
     <row r="331">
@@ -6053,16 +6053,16 @@
         <v>29</v>
       </c>
       <c r="B331" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C331" t="n">
-        <v>720.5</v>
+        <v>151.2</v>
       </c>
       <c r="D331" t="n">
-        <v>6904</v>
+        <v>302</v>
       </c>
       <c r="E331" t="n">
-        <v>2062.144866395181</v>
+        <v>67.38070940558582</v>
       </c>
     </row>
     <row r="332">
@@ -6070,16 +6070,16 @@
         <v>30</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C332" t="n">
-        <v>50.4</v>
+        <v>121.1</v>
       </c>
       <c r="D332" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E332" t="n">
-        <v>81.11991124255499</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="333">
@@ -6087,16 +6087,16 @@
         <v>31</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C333" t="n">
-        <v>30.3</v>
+        <v>661.6</v>
       </c>
       <c r="D333" t="n">
-        <v>102</v>
+        <v>5305</v>
       </c>
       <c r="E333" t="n">
-        <v>46.28617504179839</v>
+        <v>1549.828842162901</v>
       </c>
     </row>
     <row r="334">
@@ -6104,16 +6104,16 @@
         <v>32</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C334" t="n">
-        <v>140.3</v>
+        <v>200.9</v>
       </c>
       <c r="D334" t="n">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="E334" t="n">
-        <v>297.651154877652</v>
+        <v>236.3473926236547</v>
       </c>
     </row>
     <row r="335">
@@ -6121,16 +6121,16 @@
         <v>33</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C335" t="n">
-        <v>70.40000000000001</v>
+        <v>211.1</v>
       </c>
       <c r="D335" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E335" t="n">
-        <v>90.46678948652925</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="336">
@@ -6138,16 +6138,16 @@
         <v>34</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C336" t="n">
-        <v>20.1</v>
+        <v>271</v>
       </c>
       <c r="D336" t="n">
-        <v>201</v>
+        <v>1701</v>
       </c>
       <c r="E336" t="n">
-        <v>60.3</v>
+        <v>477.5981574503821</v>
       </c>
     </row>
     <row r="337">
@@ -6155,16 +6155,16 @@
         <v>35</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C337" t="n">
-        <v>20.1</v>
+        <v>181.3</v>
       </c>
       <c r="D337" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E337" t="n">
-        <v>60.3</v>
+        <v>125.2685515203237</v>
       </c>
     </row>
     <row r="338">
@@ -6172,16 +6172,16 @@
         <v>36</v>
       </c>
       <c r="B338" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C338" t="n">
-        <v>140.3</v>
+        <v>361.1</v>
       </c>
       <c r="D338" t="n">
-        <v>1001</v>
+        <v>2601</v>
       </c>
       <c r="E338" t="n">
-        <v>294.2383557594081</v>
+        <v>747.2403160965019</v>
       </c>
     </row>
     <row r="339">
@@ -6189,16 +6189,16 @@
         <v>37</v>
       </c>
       <c r="B339" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C339" t="n">
-        <v>10</v>
+        <v>141.1</v>
       </c>
       <c r="D339" t="n">
-        <v>100</v>
+        <v>502</v>
       </c>
       <c r="E339" t="n">
-        <v>30</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="340">
@@ -6206,16 +6206,16 @@
         <v>38</v>
       </c>
       <c r="B340" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C340" t="n">
-        <v>80.3</v>
+        <v>331.1</v>
       </c>
       <c r="D340" t="n">
-        <v>301</v>
+        <v>1102</v>
       </c>
       <c r="E340" t="n">
-        <v>108.1305229803315</v>
+        <v>358.0143712199275</v>
       </c>
     </row>
     <row r="341">
@@ -6223,16 +6223,16 @@
         <v>39</v>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C341" t="n">
-        <v>55365793.7</v>
+        <v>45612203.6</v>
       </c>
       <c r="D341" t="n">
-        <v>155926897</v>
+        <v>130181074</v>
       </c>
       <c r="E341" t="n">
-        <v>42829203.6573844</v>
+        <v>38934065.43548799</v>
       </c>
     </row>
     <row r="342">
@@ -6240,16 +6240,16 @@
         <v>40</v>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C342" t="n">
-        <v>16998771.2</v>
+        <v>2202841</v>
       </c>
       <c r="D342" t="n">
-        <v>53017551</v>
+        <v>6650951</v>
       </c>
       <c r="E342" t="n">
-        <v>17874614.03917097</v>
+        <v>2701862.813559637</v>
       </c>
     </row>
     <row r="343">
@@ -6257,16 +6257,16 @@
         <v>41</v>
       </c>
       <c r="B343" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C343" t="n">
-        <v>5293000.7</v>
+        <v>545892.3</v>
       </c>
       <c r="D343" t="n">
-        <v>14726681</v>
+        <v>5070907</v>
       </c>
       <c r="E343" t="n">
-        <v>5756620.231549239</v>
+        <v>1509403.120111394</v>
       </c>
     </row>
     <row r="344">
@@ -6274,16 +6274,16 @@
         <v>42</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C344" t="n">
-        <v>2254574</v>
+        <v>12784.7</v>
       </c>
       <c r="D344" t="n">
-        <v>16354475</v>
+        <v>126535</v>
       </c>
       <c r="E344" t="n">
-        <v>4788881.42978955</v>
+        <v>37916.82305006579</v>
       </c>
     </row>
     <row r="345">
@@ -6291,16 +6291,16 @@
         <v>43</v>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C345" t="n">
-        <v>207692.4</v>
+        <v>2632</v>
       </c>
       <c r="D345" t="n">
-        <v>2057223</v>
+        <v>22610</v>
       </c>
       <c r="E345" t="n">
-        <v>616537.8586715012</v>
+        <v>6677.233513963698</v>
       </c>
     </row>
     <row r="346">
@@ -6308,16 +6308,16 @@
         <v>44</v>
       </c>
       <c r="B346" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C346" t="n">
-        <v>30.1</v>
+        <v>200.9</v>
       </c>
       <c r="D346" t="n">
-        <v>301</v>
+        <v>900</v>
       </c>
       <c r="E346" t="n">
-        <v>90.3</v>
+        <v>236.3473926236547</v>
       </c>
     </row>
     <row r="347">
@@ -6325,16 +6325,16 @@
         <v>45</v>
       </c>
       <c r="B347" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C347" t="n">
-        <v>10.1</v>
+        <v>101</v>
       </c>
       <c r="D347" t="n">
         <v>101</v>
       </c>
       <c r="E347" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -6342,16 +6342,16 @@
         <v>46</v>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C348" t="n">
-        <v>60.4</v>
+        <v>881.5</v>
       </c>
       <c r="D348" t="n">
-        <v>202</v>
+        <v>6905</v>
       </c>
       <c r="E348" t="n">
-        <v>92.26288527896794</v>
+        <v>2025.448456515248</v>
       </c>
     </row>
     <row r="349">
@@ -6359,16 +6359,16 @@
         <v>47</v>
       </c>
       <c r="B349" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C349" t="n">
-        <v>120.3</v>
+        <v>121.1</v>
       </c>
       <c r="D349" t="n">
-        <v>901</v>
+        <v>202</v>
       </c>
       <c r="E349" t="n">
-        <v>267.8958939588287</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="350">
@@ -6376,16 +6376,16 @@
         <v>48</v>
       </c>
       <c r="B350" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C350" t="n">
-        <v>30.4</v>
+        <v>161.5</v>
       </c>
       <c r="D350" t="n">
-        <v>102</v>
+        <v>302</v>
       </c>
       <c r="E350" t="n">
-        <v>46.43748485867855</v>
+        <v>66.78510312936561</v>
       </c>
     </row>
     <row r="351">
@@ -6393,16 +6393,16 @@
         <v>49</v>
       </c>
       <c r="B351" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C351" t="n">
-        <v>130.3</v>
+        <v>882</v>
       </c>
       <c r="D351" t="n">
-        <v>1102</v>
+        <v>7608</v>
       </c>
       <c r="E351" t="n">
-        <v>329.397040059561</v>
+        <v>2242.909806479075</v>
       </c>
     </row>
     <row r="352">
@@ -6410,16 +6410,16 @@
         <v>50</v>
       </c>
       <c r="B352" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C352" t="n">
-        <v>750.5</v>
+        <v>101</v>
       </c>
       <c r="D352" t="n">
-        <v>6404</v>
+        <v>101</v>
       </c>
       <c r="E352" t="n">
-        <v>1912.875178886484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -6427,16 +6427,16 @@
         <v>51</v>
       </c>
       <c r="B353" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C353" t="n">
-        <v>20.1</v>
+        <v>271.1</v>
       </c>
       <c r="D353" t="n">
-        <v>201</v>
+        <v>1802</v>
       </c>
       <c r="E353" t="n">
-        <v>60.3</v>
+        <v>510.3</v>
       </c>
     </row>
     <row r="354">
@@ -6444,16 +6444,16 @@
         <v>52</v>
       </c>
       <c r="B354" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C354" t="n">
-        <v>30.2</v>
+        <v>180.9</v>
       </c>
       <c r="D354" t="n">
-        <v>201</v>
+        <v>900</v>
       </c>
       <c r="E354" t="n">
-        <v>64.40621088062859</v>
+        <v>239.7</v>
       </c>
     </row>
     <row r="355">
@@ -6461,16 +6461,16 @@
         <v>53</v>
       </c>
       <c r="B355" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C355" t="n">
-        <v>50.2</v>
+        <v>231.3</v>
       </c>
       <c r="D355" t="n">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E355" t="n">
-        <v>80.99481464884033</v>
+        <v>296.8205013135043</v>
       </c>
     </row>
     <row r="356">
@@ -6478,16 +6478,16 @@
         <v>54</v>
       </c>
       <c r="B356" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C356" t="n">
-        <v>210.4</v>
+        <v>1381.7</v>
       </c>
       <c r="D356" t="n">
-        <v>1802</v>
+        <v>6905</v>
       </c>
       <c r="E356" t="n">
-        <v>534.333641089535</v>
+        <v>2070.490282517645</v>
       </c>
     </row>
     <row r="357">
@@ -6495,16 +6495,16 @@
         <v>55</v>
       </c>
       <c r="B357" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C357" t="n">
-        <v>100.1</v>
+        <v>101</v>
       </c>
       <c r="D357" t="n">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="E357" t="n">
-        <v>300.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -6512,16 +6512,16 @@
         <v>56</v>
       </c>
       <c r="B358" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C358" t="n">
-        <v>40.2</v>
+        <v>101</v>
       </c>
       <c r="D358" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E358" t="n">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -6529,16 +6529,16 @@
         <v>57</v>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C359" t="n">
-        <v>140.2</v>
+        <v>121.2</v>
       </c>
       <c r="D359" t="n">
-        <v>1402</v>
+        <v>202</v>
       </c>
       <c r="E359" t="n">
-        <v>420.6</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="360">
@@ -6546,16 +6546,16 @@
         <v>58</v>
       </c>
       <c r="B360" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C360" t="n">
-        <v>650.5</v>
+        <v>961.7</v>
       </c>
       <c r="D360" t="n">
-        <v>6404</v>
+        <v>6905</v>
       </c>
       <c r="E360" t="n">
-        <v>1918.069719796442</v>
+        <v>2004.738738589146</v>
       </c>
     </row>
     <row r="361">
@@ -6563,16 +6563,16 @@
         <v>59</v>
       </c>
       <c r="B361" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C361" t="n">
-        <v>45384173.6</v>
+        <v>49383194.1</v>
       </c>
       <c r="D361" t="n">
-        <v>127109991</v>
+        <v>145256906</v>
       </c>
       <c r="E361" t="n">
-        <v>33815100.71702592</v>
+        <v>41820320.39208513</v>
       </c>
     </row>
     <row r="362">
@@ -6580,16 +6580,16 @@
         <v>60</v>
       </c>
       <c r="B362" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C362" t="n">
-        <v>23109845.5</v>
+        <v>21235339.1</v>
       </c>
       <c r="D362" t="n">
-        <v>54683782</v>
+        <v>64741535</v>
       </c>
       <c r="E362" t="n">
-        <v>23663087.98621554</v>
+        <v>20818839.14587926</v>
       </c>
     </row>
     <row r="363">
@@ -6597,16 +6597,16 @@
         <v>61</v>
       </c>
       <c r="B363" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C363" t="n">
-        <v>11581302</v>
+        <v>1798410</v>
       </c>
       <c r="D363" t="n">
-        <v>40810798</v>
+        <v>15318494</v>
       </c>
       <c r="E363" t="n">
-        <v>17683546.95253456</v>
+        <v>4523422.995526706</v>
       </c>
     </row>
     <row r="364">
@@ -6614,16 +6614,16 @@
         <v>62</v>
       </c>
       <c r="B364" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C364" t="n">
-        <v>3751741.1</v>
+        <v>23986.4</v>
       </c>
       <c r="D364" t="n">
-        <v>37435394</v>
+        <v>227450</v>
       </c>
       <c r="E364" t="n">
-        <v>11227893.73547078</v>
+        <v>67842.67556368926</v>
       </c>
     </row>
     <row r="365">
@@ -6631,16 +6631,16 @@
         <v>63</v>
       </c>
       <c r="B365" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C365" t="n">
-        <v>700.5</v>
+        <v>421.4</v>
       </c>
       <c r="D365" t="n">
-        <v>6804</v>
+        <v>2904</v>
       </c>
       <c r="E365" t="n">
-        <v>2035.382384221697</v>
+        <v>831.3030975522706</v>
       </c>
     </row>
     <row r="366">
@@ -6648,16 +6648,16 @@
         <v>64</v>
       </c>
       <c r="B366" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C366" t="n">
-        <v>150.2</v>
+        <v>211.1</v>
       </c>
       <c r="D366" t="n">
-        <v>1302</v>
+        <v>1001</v>
       </c>
       <c r="E366" t="n">
-        <v>385.9538314358338</v>
+        <v>270.0334979220171</v>
       </c>
     </row>
     <row r="367">
@@ -6665,16 +6665,16 @@
         <v>65</v>
       </c>
       <c r="B367" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C367" t="n">
-        <v>180.5</v>
+        <v>101</v>
       </c>
       <c r="D367" t="n">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="E367" t="n">
-        <v>289.4481818909906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -6682,16 +6682,16 @@
         <v>66</v>
       </c>
       <c r="B368" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C368" t="n">
-        <v>140.4</v>
+        <v>131.1</v>
       </c>
       <c r="D368" t="n">
-        <v>1001</v>
+        <v>202</v>
       </c>
       <c r="E368" t="n">
-        <v>297.6716983523963</v>
+        <v>45.97923444338759</v>
       </c>
     </row>
     <row r="369">
@@ -6699,16 +6699,16 @@
         <v>67</v>
       </c>
       <c r="B369" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C369" t="n">
-        <v>210.3</v>
+        <v>371.3</v>
       </c>
       <c r="D369" t="n">
-        <v>1001</v>
+        <v>1701</v>
       </c>
       <c r="E369" t="n">
-        <v>375.7581802170114</v>
+        <v>515.9054273798639</v>
       </c>
     </row>
     <row r="370">
@@ -6716,16 +6716,16 @@
         <v>68</v>
       </c>
       <c r="B370" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C370" t="n">
-        <v>40.2</v>
+        <v>321.5</v>
       </c>
       <c r="D370" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E370" t="n">
-        <v>80.40000000000001</v>
+        <v>371.2687032325779</v>
       </c>
     </row>
     <row r="371">
@@ -6733,16 +6733,16 @@
         <v>69</v>
       </c>
       <c r="B371" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C371" t="n">
-        <v>40.2</v>
+        <v>101</v>
       </c>
       <c r="D371" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E371" t="n">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -6750,16 +6750,16 @@
         <v>70</v>
       </c>
       <c r="B372" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C372" t="n">
-        <v>40.2</v>
+        <v>171.3</v>
       </c>
       <c r="D372" t="n">
-        <v>201</v>
+        <v>502</v>
       </c>
       <c r="E372" t="n">
-        <v>80.40000000000001</v>
+        <v>127.2721886352238</v>
       </c>
     </row>
     <row r="373">
@@ -6767,16 +6767,16 @@
         <v>71</v>
       </c>
       <c r="B373" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C373" t="n">
-        <v>70.3</v>
+        <v>121.1</v>
       </c>
       <c r="D373" t="n">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="E373" t="n">
-        <v>127.508470306878</v>
+        <v>40.20062188573704</v>
       </c>
     </row>
     <row r="374">
@@ -6784,16 +6784,16 @@
         <v>72</v>
       </c>
       <c r="B374" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C374" t="n">
-        <v>40.2</v>
+        <v>101</v>
       </c>
       <c r="D374" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E374" t="n">
-        <v>80.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -6801,16 +6801,16 @@
         <v>73</v>
       </c>
       <c r="B375" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C375" t="n">
-        <v>140.5</v>
+        <v>101</v>
       </c>
       <c r="D375" t="n">
-        <v>901</v>
+        <v>101</v>
       </c>
       <c r="E375" t="n">
-        <v>265.6321704914523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -6818,16 +6818,16 @@
         <v>74</v>
       </c>
       <c r="B376" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C376" t="n">
-        <v>30.2</v>
+        <v>111</v>
       </c>
       <c r="D376" t="n">
         <v>201</v>
       </c>
       <c r="E376" t="n">
-        <v>64.40621088062859</v>
+        <v>30</v>
       </c>
     </row>
     <row r="377">
@@ -6835,16 +6835,16 @@
         <v>75</v>
       </c>
       <c r="B377" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C377" t="n">
-        <v>140.4</v>
+        <v>141.1</v>
       </c>
       <c r="D377" t="n">
-        <v>901</v>
+        <v>502</v>
       </c>
       <c r="E377" t="n">
-        <v>265.6468332203492</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="378">
@@ -6852,16 +6852,16 @@
         <v>76</v>
       </c>
       <c r="B378" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C378" t="n">
-        <v>50.2</v>
+        <v>101</v>
       </c>
       <c r="D378" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E378" t="n">
-        <v>80.99481464884033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -6869,16 +6869,16 @@
         <v>77</v>
       </c>
       <c r="B379" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C379" t="n">
-        <v>120.2</v>
+        <v>221</v>
       </c>
       <c r="D379" t="n">
-        <v>1101</v>
+        <v>900</v>
       </c>
       <c r="E379" t="n">
-        <v>328.3171637304392</v>
+        <v>255.9691387648128</v>
       </c>
     </row>
     <row r="380">
@@ -6886,16 +6886,16 @@
         <v>78</v>
       </c>
       <c r="B380" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C380" t="n">
-        <v>130.3</v>
+        <v>361.1</v>
       </c>
       <c r="D380" t="n">
-        <v>1001</v>
+        <v>1701</v>
       </c>
       <c r="E380" t="n">
-        <v>297.1232235958677</v>
+        <v>520.1231488791861</v>
       </c>
     </row>
     <row r="381">
@@ -6903,16 +6903,16 @@
         <v>79</v>
       </c>
       <c r="B381" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C381" t="n">
-        <v>47524513.6</v>
+        <v>41274304.8</v>
       </c>
       <c r="D381" t="n">
-        <v>150428758</v>
+        <v>80665635</v>
       </c>
       <c r="E381" t="n">
-        <v>44471227.31091324</v>
+        <v>28292163.74754404</v>
       </c>
     </row>
     <row r="382">
@@ -6920,16 +6920,16 @@
         <v>80</v>
       </c>
       <c r="B382" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C382" t="n">
-        <v>8526773.6</v>
+        <v>18814481.7</v>
       </c>
       <c r="D382" t="n">
-        <v>29881926</v>
+        <v>68400746</v>
       </c>
       <c r="E382" t="n">
-        <v>10136323.84316001</v>
+        <v>22099849.61527966</v>
       </c>
     </row>
     <row r="383">
@@ -6937,16 +6937,16 @@
         <v>81</v>
       </c>
       <c r="B383" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C383" t="n">
-        <v>1370514.7</v>
+        <v>5305116.9</v>
       </c>
       <c r="D383" t="n">
-        <v>9433350</v>
+        <v>37070281</v>
       </c>
       <c r="E383" t="n">
-        <v>2910323.918292569</v>
+        <v>11358203.11144345</v>
       </c>
     </row>
     <row r="384">
@@ -6954,16 +6954,16 @@
         <v>82</v>
       </c>
       <c r="B384" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C384" t="n">
-        <v>418576.5</v>
+        <v>149222</v>
       </c>
       <c r="D384" t="n">
-        <v>3783396</v>
+        <v>1447804</v>
       </c>
       <c r="E384" t="n">
-        <v>1127985.798039341</v>
+        <v>432963.3193971517</v>
       </c>
     </row>
     <row r="385">
@@ -6971,16 +6971,16 @@
         <v>83</v>
       </c>
       <c r="B385" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C385" t="n">
-        <v>30.2</v>
+        <v>311.1</v>
       </c>
       <c r="D385" t="n">
-        <v>201</v>
+        <v>1701</v>
       </c>
       <c r="E385" t="n">
-        <v>64.40621088062858</v>
+        <v>478.4747537749511</v>
       </c>
     </row>
     <row r="386">
@@ -6988,16 +6988,16 @@
         <v>84</v>
       </c>
       <c r="B386" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C386" t="n">
-        <v>80.2</v>
+        <v>101</v>
       </c>
       <c r="D386" t="n">
-        <v>400</v>
+        <v>101</v>
       </c>
       <c r="E386" t="n">
-        <v>125.0126393609862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -7005,16 +7005,16 @@
         <v>85</v>
       </c>
       <c r="B387" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C387" t="n">
-        <v>120.2</v>
+        <v>101</v>
       </c>
       <c r="D387" t="n">
-        <v>901</v>
+        <v>101</v>
       </c>
       <c r="E387" t="n">
-        <v>267.903266124174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -7022,16 +7022,16 @@
         <v>86</v>
       </c>
       <c r="B388" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C388" t="n">
-        <v>120.2</v>
+        <v>180.9</v>
       </c>
       <c r="D388" t="n">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E388" t="n">
-        <v>267.903266124174</v>
+        <v>239.7</v>
       </c>
     </row>
     <row r="389">
@@ -7039,16 +7039,16 @@
         <v>87</v>
       </c>
       <c r="B389" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C389" t="n">
-        <v>200.2</v>
+        <v>141.1</v>
       </c>
       <c r="D389" t="n">
-        <v>1001</v>
+        <v>502</v>
       </c>
       <c r="E389" t="n">
-        <v>400.4</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="390">
@@ -7056,16 +7056,16 @@
         <v>88</v>
       </c>
       <c r="B390" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C390" t="n">
-        <v>130.3</v>
+        <v>121</v>
       </c>
       <c r="D390" t="n">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E390" t="n">
-        <v>293.7042900605982</v>
+        <v>40</v>
       </c>
     </row>
     <row r="391">
@@ -7073,16 +7073,16 @@
         <v>89</v>
       </c>
       <c r="B391" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C391" t="n">
-        <v>30.1</v>
+        <v>111</v>
       </c>
       <c r="D391" t="n">
         <v>201</v>
       </c>
       <c r="E391" t="n">
-        <v>64.29688950485863</v>
+        <v>30</v>
       </c>
     </row>
     <row r="392">
@@ -7090,16 +7090,16 @@
         <v>90</v>
       </c>
       <c r="B392" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C392" t="n">
-        <v>120.2</v>
+        <v>181.4</v>
       </c>
       <c r="D392" t="n">
-        <v>1001</v>
+        <v>603</v>
       </c>
       <c r="E392" t="n">
-        <v>299.6533997804797</v>
+        <v>154.2609477476396</v>
       </c>
     </row>
     <row r="393">
@@ -7107,16 +7107,16 @@
         <v>91</v>
       </c>
       <c r="B393" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C393" t="n">
-        <v>20.1</v>
+        <v>761.6</v>
       </c>
       <c r="D393" t="n">
-        <v>201</v>
+        <v>2904</v>
       </c>
       <c r="E393" t="n">
-        <v>60.3</v>
+        <v>903.177081197259</v>
       </c>
     </row>
     <row r="394">
@@ -7124,16 +7124,16 @@
         <v>92</v>
       </c>
       <c r="B394" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C394" t="n">
-        <v>50.2</v>
+        <v>361.4</v>
       </c>
       <c r="D394" t="n">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E394" t="n">
-        <v>80.99481464884033</v>
+        <v>323.3456973581062</v>
       </c>
     </row>
     <row r="395">
@@ -7141,16 +7141,16 @@
         <v>93</v>
       </c>
       <c r="B395" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C395" t="n">
-        <v>220.4</v>
+        <v>251.2</v>
       </c>
       <c r="D395" t="n">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E395" t="n">
-        <v>349.0905899619754</v>
+        <v>241.7030409407378</v>
       </c>
     </row>
     <row r="396">
@@ -7158,16 +7158,16 @@
         <v>94</v>
       </c>
       <c r="B396" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C396" t="n">
-        <v>10.1</v>
+        <v>161.4</v>
       </c>
       <c r="D396" t="n">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="E396" t="n">
-        <v>30.3</v>
+        <v>80.45023306367732</v>
       </c>
     </row>
     <row r="397">
@@ -7175,16 +7175,16 @@
         <v>95</v>
       </c>
       <c r="B397" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C397" t="n">
-        <v>180.5</v>
+        <v>261.1</v>
       </c>
       <c r="D397" t="n">
-        <v>1001</v>
+        <v>1403</v>
       </c>
       <c r="E397" t="n">
-        <v>289.483073771162</v>
+        <v>383.2866942642283</v>
       </c>
     </row>
     <row r="398">
@@ -7192,16 +7192,16 @@
         <v>96</v>
       </c>
       <c r="B398" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C398" t="n">
-        <v>60.5</v>
+        <v>370.7</v>
       </c>
       <c r="D398" t="n">
-        <v>201</v>
+        <v>1401</v>
       </c>
       <c r="E398" t="n">
-        <v>80.50124222644021</v>
+        <v>431.5351781720698</v>
       </c>
     </row>
     <row r="399">
@@ -7209,16 +7209,16 @@
         <v>97</v>
       </c>
       <c r="B399" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C399" t="n">
-        <v>130.4</v>
+        <v>230.6</v>
       </c>
       <c r="D399" t="n">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="E399" t="n">
-        <v>293.6944670912273</v>
+        <v>253.0696346857916</v>
       </c>
     </row>
     <row r="400">
@@ -7226,16 +7226,16 @@
         <v>98</v>
       </c>
       <c r="B400" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C400" t="n">
-        <v>10</v>
+        <v>270.4</v>
       </c>
       <c r="D400" t="n">
-        <v>100</v>
+        <v>1701</v>
       </c>
       <c r="E400" t="n">
-        <v>30</v>
+        <v>477.8119295287634</v>
       </c>
     </row>
     <row r="401">
@@ -7243,16 +7243,16 @@
         <v>99</v>
       </c>
       <c r="B401" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C401" t="n">
-        <v>57936430.8</v>
+        <v>39025036.4</v>
       </c>
       <c r="D401" t="n">
-        <v>115583874</v>
+        <v>120579369</v>
       </c>
       <c r="E401" t="n">
-        <v>40620139.34847087</v>
+        <v>38932821.49220766</v>
       </c>
     </row>
     <row r="402">
@@ -7260,16 +7260,16 @@
         <v>0</v>
       </c>
       <c r="B402" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C402" t="n">
-        <v>32230394.1</v>
+        <v>7504563.2</v>
       </c>
       <c r="D402" t="n">
-        <v>64952158</v>
+        <v>24139984</v>
       </c>
       <c r="E402" t="n">
-        <v>22698148.7635992</v>
+        <v>9596760.525610846</v>
       </c>
     </row>
     <row r="403">
@@ -7277,16 +7277,16 @@
         <v>1</v>
       </c>
       <c r="B403" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C403" t="n">
-        <v>13593058.6</v>
+        <v>221.2</v>
       </c>
       <c r="D403" t="n">
-        <v>34462155</v>
+        <v>501</v>
       </c>
       <c r="E403" t="n">
-        <v>10699147.75023595</v>
+        <v>132.937428890437</v>
       </c>
     </row>
     <row r="404">
@@ -7294,16 +7294,16 @@
         <v>2</v>
       </c>
       <c r="B404" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C404" t="n">
-        <v>3795474.2</v>
+        <v>170.9</v>
       </c>
       <c r="D404" t="n">
-        <v>8987237</v>
+        <v>502</v>
       </c>
       <c r="E404" t="n">
-        <v>3360126.063578294</v>
+        <v>127.2567876382239</v>
       </c>
     </row>
     <row r="405">
@@ -7311,16 +7311,16 @@
         <v>3</v>
       </c>
       <c r="B405" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C405" t="n">
-        <v>1677768.7</v>
+        <v>110.4</v>
       </c>
       <c r="D405" t="n">
-        <v>6716491</v>
+        <v>201</v>
       </c>
       <c r="E405" t="n">
-        <v>2599305.944449481</v>
+        <v>30.20331107676773</v>
       </c>
     </row>
     <row r="406">
@@ -7328,16 +7328,16 @@
         <v>4</v>
       </c>
       <c r="B406" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C406" t="n">
-        <v>100.1</v>
+        <v>150.4</v>
       </c>
       <c r="D406" t="n">
-        <v>1001</v>
+        <v>301</v>
       </c>
       <c r="E406" t="n">
-        <v>300.3</v>
+        <v>80.9953085061104</v>
       </c>
     </row>
     <row r="407">
@@ -7345,16 +7345,16 @@
         <v>5</v>
       </c>
       <c r="B407" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C407" t="n">
-        <v>250.4</v>
+        <v>110.2</v>
       </c>
       <c r="D407" t="n">
-        <v>2002</v>
+        <v>201</v>
       </c>
       <c r="E407" t="n">
-        <v>592.6216668330648</v>
+        <v>30.26813505982819</v>
       </c>
     </row>
     <row r="408">
@@ -7362,16 +7362,16 @@
         <v>6</v>
       </c>
       <c r="B408" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C408" t="n">
-        <v>30.1</v>
+        <v>300.2</v>
       </c>
       <c r="D408" t="n">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E408" t="n">
-        <v>64.29688950485863</v>
+        <v>400.4</v>
       </c>
     </row>
     <row r="409">
@@ -7379,16 +7379,16 @@
         <v>7</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C409" t="n">
-        <v>60.3</v>
+        <v>200.1</v>
       </c>
       <c r="D409" t="n">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E409" t="n">
-        <v>92.10977146861238</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="410">
@@ -7396,16 +7396,16 @@
         <v>8</v>
       </c>
       <c r="B410" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C410" t="n">
-        <v>70.40000000000001</v>
+        <v>240.2</v>
       </c>
       <c r="D410" t="n">
-        <v>201</v>
+        <v>1502</v>
       </c>
       <c r="E410" t="n">
-        <v>90.46678948652925</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="411">
@@ -7413,16 +7413,16 @@
         <v>9</v>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C411" t="n">
-        <v>40.3</v>
+        <v>260.3</v>
       </c>
       <c r="D411" t="n">
-        <v>201</v>
+        <v>1101</v>
       </c>
       <c r="E411" t="n">
-        <v>66.75485001106661</v>
+        <v>297.5973958219393</v>
       </c>
     </row>
     <row r="412">
@@ -7430,16 +7430,16 @@
         <v>10</v>
       </c>
       <c r="B412" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C412" t="n">
-        <v>10</v>
+        <v>190.2</v>
       </c>
       <c r="D412" t="n">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="E412" t="n">
-        <v>30</v>
+        <v>144.8591039596753</v>
       </c>
     </row>
     <row r="413">
@@ -7447,16 +7447,16 @@
         <v>11</v>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C413" t="n">
-        <v>120.2</v>
+        <v>160.4</v>
       </c>
       <c r="D413" t="n">
-        <v>1102</v>
+        <v>301</v>
       </c>
       <c r="E413" t="n">
-        <v>328.6219104076902</v>
+        <v>80.45023306367733</v>
       </c>
     </row>
     <row r="414">
@@ -7464,16 +7464,16 @@
         <v>12</v>
       </c>
       <c r="B414" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C414" t="n">
-        <v>130.2</v>
+        <v>220.2</v>
       </c>
       <c r="D414" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="E414" t="n">
-        <v>297.133236107979</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="415">
@@ -7481,16 +7481,16 @@
         <v>13</v>
       </c>
       <c r="B415" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C415" t="n">
-        <v>20.1</v>
+        <v>100</v>
       </c>
       <c r="D415" t="n">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="E415" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -7498,16 +7498,16 @@
         <v>14</v>
       </c>
       <c r="B416" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C416" t="n">
-        <v>50.2</v>
+        <v>150.3</v>
       </c>
       <c r="D416" t="n">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E416" t="n">
-        <v>80.99481464884033</v>
+        <v>81.05683191440436</v>
       </c>
     </row>
     <row r="417">
@@ -7515,16 +7515,16 @@
         <v>15</v>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C417" t="n">
-        <v>0</v>
+        <v>150.1</v>
       </c>
       <c r="D417" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E417" t="n">
-        <v>0</v>
+        <v>102.616226786995</v>
       </c>
     </row>
     <row r="418">
@@ -7532,13 +7532,13 @@
         <v>16</v>
       </c>
       <c r="B418" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C418" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D418" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E418" t="n">
         <v>0</v>
@@ -7549,16 +7549,16 @@
         <v>17</v>
       </c>
       <c r="B419" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C419" t="n">
-        <v>130.2</v>
+        <v>220.2</v>
       </c>
       <c r="D419" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="E419" t="n">
-        <v>303.822579806044</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="420">
@@ -7566,13 +7566,13 @@
         <v>18</v>
       </c>
       <c r="B420" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C420" t="n">
-        <v>20.1</v>
+        <v>120.1</v>
       </c>
       <c r="D420" t="n">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E420" t="n">
         <v>60.3</v>
@@ -7583,16 +7583,16 @@
         <v>19</v>
       </c>
       <c r="B421" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C421" t="n">
-        <v>73358347.59999999</v>
+        <v>79771050.5</v>
       </c>
       <c r="D421" t="n">
-        <v>210396724</v>
+        <v>138027948</v>
       </c>
       <c r="E421" t="n">
-        <v>63207914.19567998</v>
+        <v>49738627.89250825</v>
       </c>
     </row>
     <row r="422">
@@ -7600,16 +7600,16 @@
         <v>20</v>
       </c>
       <c r="B422" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C422" t="n">
-        <v>15121316.2</v>
+        <v>26846584.4</v>
       </c>
       <c r="D422" t="n">
-        <v>81581559</v>
+        <v>104672561</v>
       </c>
       <c r="E422" t="n">
-        <v>24423133.41948184</v>
+        <v>35808136.71596058</v>
       </c>
     </row>
     <row r="423">
@@ -7617,16 +7617,16 @@
         <v>21</v>
       </c>
       <c r="B423" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C423" t="n">
-        <v>3424901.5</v>
+        <v>3897245</v>
       </c>
       <c r="D423" t="n">
-        <v>18155105</v>
+        <v>10624115</v>
       </c>
       <c r="E423" t="n">
-        <v>6739488.75510305</v>
+        <v>4564233.101959386</v>
       </c>
     </row>
     <row r="424">
@@ -7637,13 +7637,13 @@
         <v>0</v>
       </c>
       <c r="C424" t="n">
-        <v>54680.2</v>
+        <v>210903.1</v>
       </c>
       <c r="D424" t="n">
-        <v>396949</v>
+        <v>688274</v>
       </c>
       <c r="E424" t="n">
-        <v>122476.3853098221</v>
+        <v>291428.2637375621</v>
       </c>
     </row>
     <row r="425">
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="C425" t="n">
-        <v>150.4</v>
+        <v>250.6</v>
       </c>
       <c r="D425" t="n">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E425" t="n">
-        <v>326.9563273588691</v>
+        <v>350.4574724556462</v>
       </c>
     </row>
     <row r="426">
@@ -7671,13 +7671,13 @@
         <v>0</v>
       </c>
       <c r="C426" t="n">
-        <v>0</v>
+        <v>100.3</v>
       </c>
       <c r="D426" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E426" t="n">
-        <v>0</v>
+        <v>134.3882807390585</v>
       </c>
     </row>
     <row r="427">
@@ -7688,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="C427" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="D427" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E427" t="n">
-        <v>0</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="428">
@@ -7705,13 +7705,13 @@
         <v>0</v>
       </c>
       <c r="C428" t="n">
-        <v>40.2</v>
+        <v>60.4</v>
       </c>
       <c r="D428" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E428" t="n">
-        <v>80.40000000000001</v>
+        <v>92.26288527896794</v>
       </c>
     </row>
     <row r="429">
@@ -7722,13 +7722,13 @@
         <v>0</v>
       </c>
       <c r="C429" t="n">
-        <v>110.3</v>
+        <v>50.2</v>
       </c>
       <c r="D429" t="n">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E429" t="n">
-        <v>298.4533631909683</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="430">
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="C430" t="n">
-        <v>10.1</v>
+        <v>140.3</v>
       </c>
       <c r="D430" t="n">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E430" t="n">
-        <v>30.3</v>
+        <v>300.9920430841985</v>
       </c>
     </row>
     <row r="431">
@@ -7773,13 +7773,13 @@
         <v>0</v>
       </c>
       <c r="C432" t="n">
-        <v>10.1</v>
+        <v>60.3</v>
       </c>
       <c r="D432" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E432" t="n">
-        <v>30.3</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="433">
@@ -7790,13 +7790,13 @@
         <v>0</v>
       </c>
       <c r="C433" t="n">
-        <v>150.3</v>
+        <v>150.4</v>
       </c>
       <c r="D433" t="n">
-        <v>1402</v>
+        <v>1001</v>
       </c>
       <c r="E433" t="n">
-        <v>418.3185508676373</v>
+        <v>294.4150811354609</v>
       </c>
     </row>
     <row r="434">
@@ -7807,13 +7807,13 @@
         <v>0</v>
       </c>
       <c r="C434" t="n">
-        <v>30.2</v>
+        <v>10.1</v>
       </c>
       <c r="D434" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E434" t="n">
-        <v>64.40621088062859</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="435">
@@ -7824,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="C435" t="n">
-        <v>20.1</v>
+        <v>120.2</v>
       </c>
       <c r="D435" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E435" t="n">
-        <v>60.3</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="436">
@@ -7841,13 +7841,13 @@
         <v>0</v>
       </c>
       <c r="C436" t="n">
-        <v>140.3</v>
+        <v>150.4</v>
       </c>
       <c r="D436" t="n">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="E436" t="n">
-        <v>297.6511548776521</v>
+        <v>265.8575558452308</v>
       </c>
     </row>
     <row r="437">
@@ -7858,13 +7858,13 @@
         <v>0</v>
       </c>
       <c r="C437" t="n">
-        <v>160.4</v>
+        <v>0</v>
       </c>
       <c r="D437" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="E437" t="n">
-        <v>294.2655943191456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -7875,13 +7875,13 @@
         <v>0</v>
       </c>
       <c r="C438" t="n">
-        <v>50.2</v>
+        <v>20.1</v>
       </c>
       <c r="D438" t="n">
         <v>201</v>
       </c>
       <c r="E438" t="n">
-        <v>80.99481464884033</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="439">
@@ -7892,13 +7892,13 @@
         <v>0</v>
       </c>
       <c r="C439" t="n">
-        <v>50.2</v>
+        <v>120.2</v>
       </c>
       <c r="D439" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E439" t="n">
-        <v>80.99481464884033</v>
+        <v>299.6533997804797</v>
       </c>
     </row>
     <row r="440">
@@ -7909,13 +7909,13 @@
         <v>0</v>
       </c>
       <c r="C440" t="n">
-        <v>110.2</v>
+        <v>30.2</v>
       </c>
       <c r="D440" t="n">
-        <v>901</v>
+        <v>201</v>
       </c>
       <c r="E440" t="n">
-        <v>270.3260253841646</v>
+        <v>64.40621088062859</v>
       </c>
     </row>
     <row r="441">
@@ -7926,13 +7926,13 @@
         <v>0</v>
       </c>
       <c r="C441" t="n">
-        <v>64679852.4</v>
+        <v>70939883.40000001</v>
       </c>
       <c r="D441" t="n">
-        <v>167231291</v>
+        <v>146562013</v>
       </c>
       <c r="E441" t="n">
-        <v>48430825.363823</v>
+        <v>45368484.92652824</v>
       </c>
     </row>
     <row r="442">
@@ -7943,13 +7943,13 @@
         <v>0</v>
       </c>
       <c r="C442" t="n">
-        <v>14548621.4</v>
+        <v>38655973.3</v>
       </c>
       <c r="D442" t="n">
-        <v>36506538</v>
+        <v>82850726</v>
       </c>
       <c r="E442" t="n">
-        <v>11397104.66252558</v>
+        <v>20520865.24668108</v>
       </c>
     </row>
     <row r="443">
@@ -7960,13 +7960,13 @@
         <v>0</v>
       </c>
       <c r="C443" t="n">
-        <v>3742563.8</v>
+        <v>30273006.9</v>
       </c>
       <c r="D443" t="n">
-        <v>12992724</v>
+        <v>54396984</v>
       </c>
       <c r="E443" t="n">
-        <v>5668772.41883189</v>
+        <v>14492073.23912972</v>
       </c>
     </row>
     <row r="444">
@@ -7977,13 +7977,13 @@
         <v>0</v>
       </c>
       <c r="C444" t="n">
-        <v>1021</v>
+        <v>15261688.3</v>
       </c>
       <c r="D444" t="n">
-        <v>6205</v>
+        <v>33268230</v>
       </c>
       <c r="E444" t="n">
-        <v>1841.510901406777</v>
+        <v>12333420.18881469</v>
       </c>
     </row>
     <row r="445">
@@ -7994,13 +7994,13 @@
         <v>0</v>
       </c>
       <c r="C445" t="n">
-        <v>2581.4</v>
+        <v>7315153.4</v>
       </c>
       <c r="D445" t="n">
-        <v>24210</v>
+        <v>25351083</v>
       </c>
       <c r="E445" t="n">
-        <v>7215.33813760658</v>
+        <v>8331240.271869157</v>
       </c>
     </row>
     <row r="446">
@@ -8011,13 +8011,13 @@
         <v>0</v>
       </c>
       <c r="C446" t="n">
-        <v>60.3</v>
+        <v>3238649.2</v>
       </c>
       <c r="D446" t="n">
-        <v>201</v>
+        <v>10462089</v>
       </c>
       <c r="E446" t="n">
-        <v>80.40031094467234</v>
+        <v>3972551.12522678</v>
       </c>
     </row>
     <row r="447">
@@ -8028,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="C447" t="n">
-        <v>100.1</v>
+        <v>382057.6</v>
       </c>
       <c r="D447" t="n">
-        <v>901</v>
+        <v>3819670</v>
       </c>
       <c r="E447" t="n">
-        <v>268.6263017651101</v>
+        <v>1145870.802644365</v>
       </c>
     </row>
     <row r="448">
@@ -8045,13 +8045,13 @@
         <v>0</v>
       </c>
       <c r="C448" t="n">
-        <v>70.3</v>
+        <v>40.3</v>
       </c>
       <c r="D448" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E448" t="n">
-        <v>78.47426329695615</v>
+        <v>49.35797807852344</v>
       </c>
     </row>
     <row r="449">
@@ -8062,13 +8062,13 @@
         <v>0</v>
       </c>
       <c r="C449" t="n">
-        <v>40.3</v>
+        <v>30.2</v>
       </c>
       <c r="D449" t="n">
         <v>302</v>
       </c>
       <c r="E449" t="n">
-        <v>92.28439738113913</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="450">
@@ -8079,13 +8079,13 @@
         <v>0</v>
       </c>
       <c r="C450" t="n">
-        <v>120.2</v>
+        <v>160.3</v>
       </c>
       <c r="D450" t="n">
-        <v>1001</v>
+        <v>1302</v>
       </c>
       <c r="E450" t="n">
-        <v>299.6533997804797</v>
+        <v>385.8295089803268</v>
       </c>
     </row>
     <row r="451">
@@ -8096,13 +8096,13 @@
         <v>0</v>
       </c>
       <c r="C451" t="n">
-        <v>50.2</v>
+        <v>30.1</v>
       </c>
       <c r="D451" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E451" t="n">
-        <v>80.99481464884033</v>
+        <v>45.9792344433876</v>
       </c>
     </row>
     <row r="452">
@@ -8113,13 +8113,13 @@
         <v>0</v>
       </c>
       <c r="C452" t="n">
-        <v>30</v>
+        <v>140.4</v>
       </c>
       <c r="D452" t="n">
-        <v>100</v>
+        <v>1001</v>
       </c>
       <c r="E452" t="n">
-        <v>45.8257569495584</v>
+        <v>301.0455779446029</v>
       </c>
     </row>
     <row r="453">
@@ -8130,13 +8130,13 @@
         <v>0</v>
       </c>
       <c r="C453" t="n">
-        <v>30.1</v>
+        <v>60.3</v>
       </c>
       <c r="D453" t="n">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="E453" t="n">
-        <v>90.29999999999998</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="454">
@@ -8147,13 +8147,13 @@
         <v>0</v>
       </c>
       <c r="C454" t="n">
-        <v>130.3</v>
+        <v>100.1</v>
       </c>
       <c r="D454" t="n">
         <v>1001</v>
       </c>
       <c r="E454" t="n">
-        <v>293.7042900605982</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="455">
@@ -8164,13 +8164,13 @@
         <v>0</v>
       </c>
       <c r="C455" t="n">
-        <v>200.2</v>
+        <v>30.2</v>
       </c>
       <c r="D455" t="n">
-        <v>1101</v>
+        <v>302</v>
       </c>
       <c r="E455" t="n">
-        <v>402.8897615973878</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="456">
@@ -8181,13 +8181,13 @@
         <v>0</v>
       </c>
       <c r="C456" t="n">
-        <v>50.2</v>
+        <v>120.2</v>
       </c>
       <c r="D456" t="n">
-        <v>201</v>
+        <v>1102</v>
       </c>
       <c r="E456" t="n">
-        <v>80.99481464884033</v>
+        <v>328.6219104076902</v>
       </c>
     </row>
     <row r="457">
@@ -8198,13 +8198,13 @@
         <v>0</v>
       </c>
       <c r="C457" t="n">
-        <v>30.2</v>
+        <v>140.3</v>
       </c>
       <c r="D457" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E457" t="n">
-        <v>64.40621088062858</v>
+        <v>297.651154877652</v>
       </c>
     </row>
     <row r="458">
@@ -8215,13 +8215,13 @@
         <v>0</v>
       </c>
       <c r="C458" t="n">
-        <v>10.1</v>
+        <v>40.3</v>
       </c>
       <c r="D458" t="n">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="E458" t="n">
-        <v>30.3</v>
+        <v>92.28439738113913</v>
       </c>
     </row>
     <row r="459">
@@ -8232,13 +8232,13 @@
         <v>0</v>
       </c>
       <c r="C459" t="n">
-        <v>30.1</v>
+        <v>10</v>
       </c>
       <c r="D459" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E459" t="n">
-        <v>45.9792344433876</v>
+        <v>30</v>
       </c>
     </row>
     <row r="460">
@@ -8249,13 +8249,13 @@
         <v>0</v>
       </c>
       <c r="C460" t="n">
-        <v>40.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D460" t="n">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="E460" t="n">
-        <v>80.60031017310044</v>
+        <v>108.3348512714168</v>
       </c>
     </row>
     <row r="461">
@@ -8266,13 +8266,13 @@
         <v>0</v>
       </c>
       <c r="C461" t="n">
-        <v>48192348.9</v>
+        <v>78399269.09999999</v>
       </c>
       <c r="D461" t="n">
-        <v>136254065</v>
+        <v>158883666</v>
       </c>
       <c r="E461" t="n">
-        <v>43771931.39061399</v>
+        <v>51640473.57413054</v>
       </c>
     </row>
     <row r="462">
@@ -8283,13 +8283,13 @@
         <v>0</v>
       </c>
       <c r="C462" t="n">
-        <v>11648971.3</v>
+        <v>37854132.6</v>
       </c>
       <c r="D462" t="n">
-        <v>52709350</v>
+        <v>90967326</v>
       </c>
       <c r="E462" t="n">
-        <v>15771739.7138377</v>
+        <v>32476021.15256181</v>
       </c>
     </row>
     <row r="463">
@@ -8300,13 +8300,13 @@
         <v>0</v>
       </c>
       <c r="C463" t="n">
-        <v>819213.9</v>
+        <v>485397.2</v>
       </c>
       <c r="D463" t="n">
-        <v>6525426</v>
+        <v>1474601</v>
       </c>
       <c r="E463" t="n">
-        <v>1911009.90409529</v>
+        <v>568786.9497952287</v>
       </c>
     </row>
     <row r="464">
@@ -8317,13 +8317,13 @@
         <v>0</v>
       </c>
       <c r="C464" t="n">
-        <v>93493.10000000001</v>
+        <v>63608.6</v>
       </c>
       <c r="D464" t="n">
-        <v>414650</v>
+        <v>401849</v>
       </c>
       <c r="E464" t="n">
-        <v>159066.2481914061</v>
+        <v>132587.6949638993</v>
       </c>
     </row>
     <row r="465">
@@ -8334,13 +8334,13 @@
         <v>0</v>
       </c>
       <c r="C465" t="n">
-        <v>6051.8</v>
+        <v>10.1</v>
       </c>
       <c r="D465" t="n">
-        <v>59216</v>
+        <v>101</v>
       </c>
       <c r="E465" t="n">
-        <v>17723.83769277974</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="466">
@@ -8351,13 +8351,13 @@
         <v>0</v>
       </c>
       <c r="C466" t="n">
-        <v>30.1</v>
+        <v>240.4</v>
       </c>
       <c r="D466" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E466" t="n">
-        <v>64.29688950485863</v>
+        <v>364.2365165658161</v>
       </c>
     </row>
     <row r="467">
@@ -8368,13 +8368,13 @@
         <v>0</v>
       </c>
       <c r="C467" t="n">
-        <v>60.3</v>
+        <v>30.1</v>
       </c>
       <c r="D467" t="n">
-        <v>402</v>
+        <v>201</v>
       </c>
       <c r="E467" t="n">
-        <v>128.7027971724002</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="468">
@@ -8385,13 +8385,13 @@
         <v>0</v>
       </c>
       <c r="C468" t="n">
-        <v>10</v>
+        <v>160.4</v>
       </c>
       <c r="D468" t="n">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="E468" t="n">
-        <v>30</v>
+        <v>323.4072355405797</v>
       </c>
     </row>
     <row r="469">
@@ -8402,13 +8402,13 @@
         <v>0</v>
       </c>
       <c r="C469" t="n">
-        <v>60.3</v>
+        <v>50.2</v>
       </c>
       <c r="D469" t="n">
         <v>201</v>
       </c>
       <c r="E469" t="n">
-        <v>80.40031094467234</v>
+        <v>80.99481464884033</v>
       </c>
     </row>
     <row r="470">
@@ -8419,13 +8419,13 @@
         <v>0</v>
       </c>
       <c r="C470" t="n">
-        <v>240.5</v>
+        <v>20.1</v>
       </c>
       <c r="D470" t="n">
-        <v>1702</v>
+        <v>201</v>
       </c>
       <c r="E470" t="n">
-        <v>492.8898964271838</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="471">
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="C471" t="n">
-        <v>240.4</v>
+        <v>20.1</v>
       </c>
       <c r="D471" t="n">
-        <v>2002</v>
+        <v>201</v>
       </c>
       <c r="E471" t="n">
-        <v>590.8201418367522</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="472">
@@ -8453,13 +8453,13 @@
         <v>0</v>
       </c>
       <c r="C472" t="n">
-        <v>30.1</v>
+        <v>100.1</v>
       </c>
       <c r="D472" t="n">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="E472" t="n">
-        <v>45.9792344433876</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="473">
@@ -8470,13 +8470,13 @@
         <v>0</v>
       </c>
       <c r="C473" t="n">
-        <v>100.1</v>
+        <v>40.3</v>
       </c>
       <c r="D473" t="n">
-        <v>1001</v>
+        <v>302</v>
       </c>
       <c r="E473" t="n">
-        <v>300.3</v>
+        <v>92.28439738113913</v>
       </c>
     </row>
     <row r="474">
@@ -8487,13 +8487,13 @@
         <v>0</v>
       </c>
       <c r="C474" t="n">
-        <v>10.1</v>
+        <v>30.1</v>
       </c>
       <c r="D474" t="n">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="E474" t="n">
-        <v>30.3</v>
+        <v>64.29688950485863</v>
       </c>
     </row>
     <row r="475">
@@ -8504,13 +8504,13 @@
         <v>0</v>
       </c>
       <c r="C475" t="n">
-        <v>10.1</v>
+        <v>60.3</v>
       </c>
       <c r="D475" t="n">
-        <v>101</v>
+        <v>402</v>
       </c>
       <c r="E475" t="n">
-        <v>30.3</v>
+        <v>128.7027971724003</v>
       </c>
     </row>
     <row r="476">
@@ -8521,13 +8521,13 @@
         <v>0</v>
       </c>
       <c r="C476" t="n">
-        <v>40.2</v>
+        <v>20.1</v>
       </c>
       <c r="D476" t="n">
         <v>201</v>
       </c>
       <c r="E476" t="n">
-        <v>80.40000000000001</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="477">
@@ -8538,13 +8538,13 @@
         <v>0</v>
       </c>
       <c r="C477" t="n">
-        <v>110.2</v>
+        <v>0</v>
       </c>
       <c r="D477" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="E477" t="n">
-        <v>298.456294957905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -8555,13 +8555,13 @@
         <v>0</v>
       </c>
       <c r="C478" t="n">
-        <v>720.6</v>
+        <v>40.2</v>
       </c>
       <c r="D478" t="n">
-        <v>6804</v>
+        <v>201</v>
       </c>
       <c r="E478" t="n">
-        <v>2029.349018774247</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="479">
@@ -8589,13 +8589,13 @@
         <v>0</v>
       </c>
       <c r="C480" t="n">
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="D480" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="E480" t="n">
-        <v>0</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="481">
@@ -8606,13 +8606,13 @@
         <v>0</v>
       </c>
       <c r="C481" t="n">
-        <v>82331253.90000001</v>
+        <v>77403193.5</v>
       </c>
       <c r="D481" t="n">
-        <v>141199697</v>
+        <v>156901197</v>
       </c>
       <c r="E481" t="n">
-        <v>44685545.53298029</v>
+        <v>54897545.77318286</v>
       </c>
     </row>
     <row r="482">
@@ -8623,13 +8623,13 @@
         <v>0</v>
       </c>
       <c r="C482" t="n">
-        <v>23872941.3</v>
+        <v>13751071.6</v>
       </c>
       <c r="D482" t="n">
-        <v>92765660</v>
+        <v>63644983</v>
       </c>
       <c r="E482" t="n">
-        <v>31943133.65560627</v>
+        <v>20681262.91918036</v>
       </c>
     </row>
     <row r="483">
@@ -8640,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="C483" t="n">
-        <v>2321810.6</v>
+        <v>297691.3</v>
       </c>
       <c r="D483" t="n">
-        <v>9487839</v>
+        <v>984690</v>
       </c>
       <c r="E483" t="n">
-        <v>3654445.742754767</v>
+        <v>439771.1171364145</v>
       </c>
     </row>
     <row r="484">
@@ -8657,13 +8657,13 @@
         <v>0</v>
       </c>
       <c r="C484" t="n">
-        <v>951285.3</v>
+        <v>6413.4</v>
       </c>
       <c r="D484" t="n">
-        <v>9089490</v>
+        <v>31013</v>
       </c>
       <c r="E484" t="n">
-        <v>2715345.532236921</v>
+        <v>12302.47923143949</v>
       </c>
     </row>
     <row r="485">
@@ -8674,13 +8674,13 @@
         <v>0</v>
       </c>
       <c r="C485" t="n">
-        <v>1501.1</v>
+        <v>210.8</v>
       </c>
       <c r="D485" t="n">
-        <v>6804</v>
+        <v>1202</v>
       </c>
       <c r="E485" t="n">
-        <v>2667.182462824769</v>
+        <v>342.4686263002788</v>
       </c>
     </row>
     <row r="486">
@@ -8691,13 +8691,13 @@
         <v>0</v>
       </c>
       <c r="C486" t="n">
-        <v>40.2</v>
+        <v>200.6</v>
       </c>
       <c r="D486" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E486" t="n">
-        <v>66.66453329919891</v>
+        <v>300.4004660449115</v>
       </c>
     </row>
     <row r="487">
@@ -8708,13 +8708,13 @@
         <v>0</v>
       </c>
       <c r="C487" t="n">
-        <v>20</v>
+        <v>40.3</v>
       </c>
       <c r="D487" t="n">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E487" t="n">
-        <v>40</v>
+        <v>66.75634801275456</v>
       </c>
     </row>
     <row r="488">
@@ -8725,13 +8725,13 @@
         <v>0</v>
       </c>
       <c r="C488" t="n">
-        <v>130.2</v>
+        <v>110.1</v>
       </c>
       <c r="D488" t="n">
         <v>1001</v>
       </c>
       <c r="E488" t="n">
-        <v>303.822579806044</v>
+        <v>298.4595282446181</v>
       </c>
     </row>
     <row r="489">
@@ -8742,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="C489" t="n">
-        <v>160.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D489" t="n">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="E489" t="n">
-        <v>307.545785209292</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="490">
@@ -8759,13 +8759,13 @@
         <v>0</v>
       </c>
       <c r="C490" t="n">
-        <v>140.3</v>
+        <v>290.7</v>
       </c>
       <c r="D490" t="n">
-        <v>1102</v>
+        <v>2103</v>
       </c>
       <c r="E490" t="n">
-        <v>326.7972001104048</v>
+        <v>609.8317882826377</v>
       </c>
     </row>
     <row r="491">
@@ -8776,13 +8776,13 @@
         <v>0</v>
       </c>
       <c r="C491" t="n">
-        <v>190.8</v>
+        <v>60.3</v>
       </c>
       <c r="D491" t="n">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="E491" t="n">
-        <v>288.265086335477</v>
+        <v>92.10977146861238</v>
       </c>
     </row>
     <row r="492">
@@ -8796,10 +8796,10 @@
         <v>50.3</v>
       </c>
       <c r="D492" t="n">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="E492" t="n">
-        <v>103.1038796554232</v>
+        <v>81.05683191440434</v>
       </c>
     </row>
     <row r="493">
@@ -8810,13 +8810,13 @@
         <v>0</v>
       </c>
       <c r="C493" t="n">
-        <v>30.2</v>
+        <v>10.1</v>
       </c>
       <c r="D493" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="E493" t="n">
-        <v>64.40621088062859</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="494">
@@ -8827,13 +8827,13 @@
         <v>0</v>
       </c>
       <c r="C494" t="n">
-        <v>40.2</v>
+        <v>60.2</v>
       </c>
       <c r="D494" t="n">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="E494" t="n">
-        <v>80.40000000000001</v>
+        <v>102.3531142662499</v>
       </c>
     </row>
     <row r="495">
@@ -8844,13 +8844,13 @@
         <v>0</v>
       </c>
       <c r="C495" t="n">
-        <v>250.3</v>
+        <v>690.4</v>
       </c>
       <c r="D495" t="n">
-        <v>2103</v>
+        <v>6804</v>
       </c>
       <c r="E495" t="n">
-        <v>628.9760011319986</v>
+        <v>2038.084747992585</v>
       </c>
     </row>
     <row r="496">
@@ -8861,13 +8861,13 @@
         <v>0</v>
       </c>
       <c r="C496" t="n">
-        <v>30.2</v>
+        <v>240.4</v>
       </c>
       <c r="D496" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E496" t="n">
-        <v>64.40621088062858</v>
+        <v>364.2365165658161</v>
       </c>
     </row>
     <row r="497">
@@ -8878,13 +8878,13 @@
         <v>0</v>
       </c>
       <c r="C497" t="n">
-        <v>40.3</v>
+        <v>140.3</v>
       </c>
       <c r="D497" t="n">
-        <v>202</v>
+        <v>1102</v>
       </c>
       <c r="E497" t="n">
-        <v>80.60031017310044</v>
+        <v>326.7972001104048</v>
       </c>
     </row>
     <row r="498">
@@ -8895,13 +8895,13 @@
         <v>0</v>
       </c>
       <c r="C498" t="n">
-        <v>20.1</v>
+        <v>140.2</v>
       </c>
       <c r="D498" t="n">
-        <v>201</v>
+        <v>1001</v>
       </c>
       <c r="E498" t="n">
-        <v>60.3</v>
+        <v>294.2518649048804</v>
       </c>
     </row>
     <row r="499">
@@ -8912,13 +8912,13 @@
         <v>0</v>
       </c>
       <c r="C499" t="n">
-        <v>120.2</v>
+        <v>20.1</v>
       </c>
       <c r="D499" t="n">
-        <v>1001</v>
+        <v>101</v>
       </c>
       <c r="E499" t="n">
-        <v>299.6533997804797</v>
+        <v>40.20062188573705</v>
       </c>
     </row>
     <row r="500">
@@ -8929,13 +8929,13 @@
         <v>0</v>
       </c>
       <c r="C500" t="n">
-        <v>80.40000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="D500" t="n">
         <v>201</v>
       </c>
       <c r="E500" t="n">
-        <v>98.46948765988377</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="501">
@@ -8946,13 +8946,13 @@
         <v>0</v>
       </c>
       <c r="C501" t="n">
-        <v>55630376.7</v>
+        <v>74733175.8</v>
       </c>
       <c r="D501" t="n">
-        <v>98465439</v>
+        <v>163813718</v>
       </c>
       <c r="E501" t="n">
-        <v>34026726.47831749</v>
+        <v>50272619.82907287</v>
       </c>
     </row>
   </sheetData>
